--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -554,7 +554,7 @@
   <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12.8828" customWidth="1" style="10" min="9" max="9"/>
+    <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2485,7 +2485,7 @@
     <col width="16.4922" customWidth="1" style="20" min="4" max="4"/>
     <col width="19.082" customWidth="1" style="20" min="5" max="5"/>
     <col width="8.29297" customWidth="1" style="20" min="6" max="6"/>
-    <col width="11.8906" customWidth="1" style="10" min="7" max="7"/>
+    <col width="11.8906" customWidth="1" style="17" min="7" max="7"/>
     <col width="10.0898" customWidth="1" style="20" min="8" max="8"/>
     <col width="15.4922" customWidth="1" style="20" min="9" max="9"/>
   </cols>
@@ -2562,7 +2562,7 @@
       <c r="H2" s="20" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I2" s="10" t="inlineStr"/>
+      <c r="I2" s="17" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="20" t="inlineStr">
@@ -2590,14 +2590,14 @@
         <f>=E3-E2</f>
         <v/>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="17">
         <f>=F3/E2</f>
         <v/>
       </c>
       <c r="H3" s="20" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="17">
         <f>=F3/H3</f>
         <v/>
       </c>
@@ -2628,14 +2628,14 @@
         <f>=E4-E3</f>
         <v/>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="17">
         <f>=F4/E3</f>
         <v/>
       </c>
       <c r="H4" s="20" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="17">
         <f>=F4/H4</f>
         <v/>
       </c>
@@ -2666,14 +2666,14 @@
         <f>=E5-E4</f>
         <v/>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="17">
         <f>=F5/E4</f>
         <v/>
       </c>
       <c r="H5" s="20" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="17">
         <f>=F5/H5</f>
         <v/>
       </c>
@@ -2704,14 +2704,14 @@
         <f>=E6-E5</f>
         <v/>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="17">
         <f>=F6/E5</f>
         <v/>
       </c>
       <c r="H6" s="20" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="17">
         <f>=F6/H6</f>
         <v/>
       </c>
@@ -2742,14 +2742,14 @@
         <f>=E7-E6</f>
         <v/>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="17">
         <f>=F7/E6</f>
         <v/>
       </c>
       <c r="H7" s="20" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="17">
         <f>=F7/H7</f>
         <v/>
       </c>
@@ -2780,14 +2780,14 @@
         <f>=E8-E7</f>
         <v/>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="17">
         <f>=F8/E7</f>
         <v/>
       </c>
       <c r="H8" s="20" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="17">
         <f>=F8/H8</f>
         <v/>
       </c>
@@ -2818,14 +2818,14 @@
         <f>=E9-E8</f>
         <v/>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="17">
         <f>=F9/E8</f>
         <v/>
       </c>
       <c r="H9" s="20" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="17">
         <f>=F9/H9</f>
         <v/>
       </c>
@@ -2856,14 +2856,14 @@
         <f>=E10-E9</f>
         <v/>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="17">
         <f>=F10/E9</f>
         <v/>
       </c>
       <c r="H10" s="20" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="17">
         <f>=F10/H10</f>
         <v/>
       </c>
@@ -2894,14 +2894,14 @@
         <f>=E11-E10</f>
         <v/>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="17">
         <f>=F11/E10</f>
         <v/>
       </c>
       <c r="H11" s="20" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="17">
         <f>=F11/H11</f>
         <v/>
       </c>
@@ -2932,14 +2932,14 @@
         <f>=E12-E11</f>
         <v/>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="17">
         <f>=F12/E11</f>
         <v/>
       </c>
       <c r="H12" s="20" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="17">
         <f>=F12/H12</f>
         <v/>
       </c>
@@ -2970,14 +2970,14 @@
         <f>=E13-E12</f>
         <v/>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="17">
         <f>=F13/E12</f>
         <v/>
       </c>
       <c r="H13" s="20" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="17">
         <f>=F13/H13</f>
         <v/>
       </c>
@@ -3008,14 +3008,14 @@
         <f>=E14-E13</f>
         <v/>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="17">
         <f>=F14/E13</f>
         <v/>
       </c>
       <c r="H14" s="20" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="17">
         <f>=F14/H14</f>
         <v/>
       </c>
@@ -3046,14 +3046,14 @@
         <f>=E15-E14</f>
         <v/>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="17">
         <f>=F15/E14</f>
         <v/>
       </c>
       <c r="H15" s="20" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="17">
         <f>=F15/H15</f>
         <v/>
       </c>
@@ -3084,14 +3084,14 @@
         <f>=E16-E15</f>
         <v/>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="17">
         <f>=F16/E15</f>
         <v/>
       </c>
       <c r="H16" s="20" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I16" s="17">
         <f>=F16/H16</f>
         <v/>
       </c>
@@ -3122,14 +3122,14 @@
         <f>=E17-E16</f>
         <v/>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="17">
         <f>=F17/E16</f>
         <v/>
       </c>
       <c r="H17" s="20" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="17">
         <f>=F17/H17</f>
         <v/>
       </c>
@@ -3160,14 +3160,14 @@
         <f>=E18-E17</f>
         <v/>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="17">
         <f>=F18/E17</f>
         <v/>
       </c>
       <c r="H18" s="20" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I18" s="17">
         <f>=F18/H18</f>
         <v/>
       </c>
@@ -3198,14 +3198,14 @@
         <f>=E19-E18</f>
         <v/>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="17">
         <f>=F19/E18</f>
         <v/>
       </c>
       <c r="H19" s="20" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="17">
         <f>=F19/H19</f>
         <v/>
       </c>
@@ -3236,14 +3236,14 @@
         <f>=E20-E19</f>
         <v/>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="17">
         <f>=F20/E19</f>
         <v/>
       </c>
       <c r="H20" s="20" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="17">
         <f>=F20/H20</f>
         <v/>
       </c>
@@ -3274,14 +3274,14 @@
         <f>=E21-E20</f>
         <v/>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="17">
         <f>=F21/E20</f>
         <v/>
       </c>
       <c r="H21" s="20" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="17">
         <f>=F21/H21</f>
         <v/>
       </c>
@@ -3312,14 +3312,14 @@
         <f>=E22-E21</f>
         <v/>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="17">
         <f>=F22/E21</f>
         <v/>
       </c>
       <c r="H22" s="20" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="17">
         <f>=F22/H22</f>
         <v/>
       </c>
@@ -3350,14 +3350,14 @@
         <f>=E23-E22</f>
         <v/>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="17">
         <f>=F23/E22</f>
         <v/>
       </c>
       <c r="H23" s="20" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I23" s="10">
+      <c r="I23" s="17">
         <f>=F23/H23</f>
         <v/>
       </c>
@@ -3388,14 +3388,14 @@
         <f>=E24-E23</f>
         <v/>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="17">
         <f>=F24/E23</f>
         <v/>
       </c>
       <c r="H24" s="20" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I24" s="10">
+      <c r="I24" s="17">
         <f>=F24/H24</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -103,7 +103,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -173,6 +173,7 @@
     <xf numFmtId="165" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -551,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -1501,6 +1502,44 @@
       </c>
       <c r="I25" s="16">
         <f>=F25/H25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E26" t="n">
+        <v>763536.6800000001</v>
+      </c>
+      <c r="F26">
+        <f>E26-E25</f>
+        <v/>
+      </c>
+      <c r="G26">
+        <f>F26/E25</f>
+        <v/>
+      </c>
+      <c r="H26" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I26">
+        <f>F26/H26</f>
         <v/>
       </c>
     </row>
@@ -1515,7 +1554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2462,6 +2501,44 @@
       </c>
       <c r="I25" s="20">
         <f>=F25/H25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E26" t="n">
+        <v>661251.66</v>
+      </c>
+      <c r="F26">
+        <f>E26-E25</f>
+        <v/>
+      </c>
+      <c r="G26">
+        <f>F26/E25</f>
+        <v/>
+      </c>
+      <c r="H26" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I26">
+        <f>F26/H26</f>
         <v/>
       </c>
     </row>
@@ -2476,7 +2553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -3435,6 +3512,44 @@
       </c>
       <c r="I25" s="20">
         <f>=F25/H25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2653068.77</v>
+      </c>
+      <c r="F26">
+        <f>E26-E25</f>
+        <v/>
+      </c>
+      <c r="G26">
+        <f>F26/E25</f>
+        <v/>
+      </c>
+      <c r="H26" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I26">
+        <f>F26/H26</f>
         <v/>
       </c>
     </row>
@@ -3537,11 +3652,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续2日增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-2+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-1+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -3578,7 +3693,7 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I3" s="13">
@@ -3619,11 +3734,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续8日增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-8+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -3660,11 +3775,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续2日减持</t>
+          <t>连续3日减持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-2+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-3+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -3679,7 +3794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4629,6 +4744,44 @@
         <v/>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1940445.49</v>
+      </c>
+      <c r="F26">
+        <f>E26-E25</f>
+        <v/>
+      </c>
+      <c r="G26">
+        <f>F26/E25</f>
+        <v/>
+      </c>
+      <c r="H26" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I26">
+        <f>F26/H26</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -1506,17 +1506,17 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -1524,21 +1524,21 @@
       <c r="D26" s="23" t="n">
         <v>46238</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="3" t="n">
         <v>763536.6800000001</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="3">
         <f>E26-E25</f>
         <v/>
       </c>
-      <c r="G26">
+      <c r="G26" s="3">
         <f>F26/E25</f>
         <v/>
       </c>
-      <c r="H26" t="n">
+      <c r="H26" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="3">
         <f>F26/H26</f>
         <v/>
       </c>
@@ -2505,17 +2505,17 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -2523,21 +2523,21 @@
       <c r="D26" s="23" t="n">
         <v>46238</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="3" t="n">
         <v>661251.66</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="3">
         <f>E26-E25</f>
         <v/>
       </c>
-      <c r="G26">
+      <c r="G26" s="3">
         <f>F26/E25</f>
         <v/>
       </c>
-      <c r="H26" t="n">
+      <c r="H26" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="3">
         <f>F26/H26</f>
         <v/>
       </c>
@@ -3516,17 +3516,17 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -3534,21 +3534,21 @@
       <c r="D26" s="23" t="n">
         <v>46238</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="3" t="n">
         <v>2653068.77</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="3">
         <f>E26-E25</f>
         <v/>
       </c>
-      <c r="G26">
+      <c r="G26" s="3">
         <f>F26/E25</f>
         <v/>
       </c>
-      <c r="H26" t="n">
+      <c r="H26" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="3">
         <f>F26/H26</f>
         <v/>
       </c>
@@ -4745,17 +4745,17 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -4763,21 +4763,21 @@
       <c r="D26" s="23" t="n">
         <v>46238</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="3" t="n">
         <v>1940445.49</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="3">
         <f>E26-E25</f>
         <v/>
       </c>
-      <c r="G26">
+      <c r="G26" s="3">
         <f>F26/E25</f>
         <v/>
       </c>
-      <c r="H26" t="n">
+      <c r="H26" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="3">
         <f>F26/H26</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -1540,6 +1540,44 @@
       </c>
       <c r="I26" s="3">
         <f>F26/H26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E27" t="n">
+        <v>714756.6800000001</v>
+      </c>
+      <c r="F27">
+        <f>E27-E26</f>
+        <v/>
+      </c>
+      <c r="G27">
+        <f>F27/E26</f>
+        <v/>
+      </c>
+      <c r="H27" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I27">
+        <f>F27/H27</f>
         <v/>
       </c>
     </row>
@@ -1554,7 +1592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2539,6 +2577,44 @@
       </c>
       <c r="I26" s="3">
         <f>F26/H26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E27" t="n">
+        <v>651801.66</v>
+      </c>
+      <c r="F27">
+        <f>E27-E26</f>
+        <v/>
+      </c>
+      <c r="G27">
+        <f>F27/E26</f>
+        <v/>
+      </c>
+      <c r="H27" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I27">
+        <f>F27/H27</f>
         <v/>
       </c>
     </row>
@@ -2553,7 +2629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -3550,6 +3626,44 @@
       </c>
       <c r="I26" s="3">
         <f>F26/H26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2593758.77</v>
+      </c>
+      <c r="F27">
+        <f>E27-E26</f>
+        <v/>
+      </c>
+      <c r="G27">
+        <f>F27/E26</f>
+        <v/>
+      </c>
+      <c r="H27" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I27">
+        <f>F27/H27</f>
         <v/>
       </c>
     </row>
@@ -3652,11 +3766,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>连续2日减持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-1+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-2+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -3693,11 +3807,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>连续2日减持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-1+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-2+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -3734,11 +3848,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>连续2日减持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -3775,11 +3889,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续3日减持</t>
+          <t>连续4日减持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-3+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-4+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -3794,7 +3908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4782,6 +4896,44 @@
         <v/>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1897845.49</v>
+      </c>
+      <c r="F27">
+        <f>E27-E26</f>
+        <v/>
+      </c>
+      <c r="G27">
+        <f>F27/E26</f>
+        <v/>
+      </c>
+      <c r="H27" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I27">
+        <f>F27/H27</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -1544,17 +1544,17 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -1562,21 +1562,21 @@
       <c r="D27" s="23" t="n">
         <v>46239</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="3" t="n">
         <v>714756.6800000001</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="3">
         <f>E27-E26</f>
         <v/>
       </c>
-      <c r="G27">
+      <c r="G27" s="3">
         <f>F27/E26</f>
         <v/>
       </c>
-      <c r="H27" t="n">
+      <c r="H27" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="3">
         <f>F27/H27</f>
         <v/>
       </c>
@@ -2581,17 +2581,17 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -2599,21 +2599,21 @@
       <c r="D27" s="23" t="n">
         <v>46239</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="3" t="n">
         <v>651801.66</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="3">
         <f>E27-E26</f>
         <v/>
       </c>
-      <c r="G27">
+      <c r="G27" s="3">
         <f>F27/E26</f>
         <v/>
       </c>
-      <c r="H27" t="n">
+      <c r="H27" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="3">
         <f>F27/H27</f>
         <v/>
       </c>
@@ -3630,17 +3630,17 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -3648,21 +3648,21 @@
       <c r="D27" s="23" t="n">
         <v>46239</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="3" t="n">
         <v>2593758.77</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="3">
         <f>E27-E26</f>
         <v/>
       </c>
-      <c r="G27">
+      <c r="G27" s="3">
         <f>F27/E26</f>
         <v/>
       </c>
-      <c r="H27" t="n">
+      <c r="H27" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="3">
         <f>F27/H27</f>
         <v/>
       </c>
@@ -4897,17 +4897,17 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -4915,21 +4915,21 @@
       <c r="D27" s="23" t="n">
         <v>46239</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="3" t="n">
         <v>1897845.49</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="3">
         <f>E27-E26</f>
         <v/>
       </c>
-      <c r="G27">
+      <c r="G27" s="3">
         <f>F27/E26</f>
         <v/>
       </c>
-      <c r="H27" t="n">
+      <c r="H27" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="3">
         <f>F27/H27</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -1578,6 +1578,44 @@
       </c>
       <c r="I27" s="3">
         <f>F27/H27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E28" t="n">
+        <v>710796.6800000001</v>
+      </c>
+      <c r="F28">
+        <f>E28-E27</f>
+        <v/>
+      </c>
+      <c r="G28">
+        <f>F28/E27</f>
+        <v/>
+      </c>
+      <c r="H28" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I28">
+        <f>F28/H28</f>
         <v/>
       </c>
     </row>
@@ -1592,7 +1630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2615,6 +2653,44 @@
       </c>
       <c r="I27" s="3">
         <f>F27/H27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E28" t="n">
+        <v>648831.66</v>
+      </c>
+      <c r="F28">
+        <f>E28-E27</f>
+        <v/>
+      </c>
+      <c r="G28">
+        <f>F28/E27</f>
+        <v/>
+      </c>
+      <c r="H28" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I28">
+        <f>F28/H28</f>
         <v/>
       </c>
     </row>
@@ -2629,7 +2705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -3664,6 +3740,44 @@
       </c>
       <c r="I27" s="3">
         <f>F27/H27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2570538.77</v>
+      </c>
+      <c r="F28">
+        <f>E28-E27</f>
+        <v/>
+      </c>
+      <c r="G28">
+        <f>F28/E27</f>
+        <v/>
+      </c>
+      <c r="H28" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I28">
+        <f>F28/H28</f>
         <v/>
       </c>
     </row>
@@ -3766,11 +3880,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续2日减持</t>
+          <t>连续3日减持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-2+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-3+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -3807,11 +3921,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续2日减持</t>
+          <t>连续3日减持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-2+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-3+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -3848,11 +3962,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续2日减持</t>
+          <t>连续3日减持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-3+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -3889,11 +4003,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续4日减持</t>
+          <t>连续5日减持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-4+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-5+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -3908,7 +4022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4934,6 +5048,44 @@
         <v/>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1876845.49</v>
+      </c>
+      <c r="F28">
+        <f>E28-E27</f>
+        <v/>
+      </c>
+      <c r="G28">
+        <f>F28/E27</f>
+        <v/>
+      </c>
+      <c r="H28" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I28">
+        <f>F28/H28</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -1582,17 +1582,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -1600,22 +1600,60 @@
       <c r="D28" s="23" t="n">
         <v>46240</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="3" t="n">
         <v>710796.6800000001</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="3">
         <f>E28-E27</f>
         <v/>
       </c>
-      <c r="G28">
+      <c r="G28" s="3">
         <f>F28/E27</f>
         <v/>
       </c>
-      <c r="H28" t="n">
+      <c r="H28" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="3">
         <f>F28/H28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="n">
+        <v>46241</v>
+      </c>
+      <c r="E29" t="n">
+        <v>689466.6800000001</v>
+      </c>
+      <c r="F29">
+        <f>E29-E28</f>
+        <v/>
+      </c>
+      <c r="G29">
+        <f>F29/E28</f>
+        <v/>
+      </c>
+      <c r="H29" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I29">
+        <f>F29/H29</f>
         <v/>
       </c>
     </row>
@@ -1630,7 +1668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2657,17 +2695,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -2675,22 +2713,60 @@
       <c r="D28" s="23" t="n">
         <v>46240</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="3" t="n">
         <v>648831.66</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="3">
         <f>E28-E27</f>
         <v/>
       </c>
-      <c r="G28">
+      <c r="G28" s="3">
         <f>F28/E27</f>
         <v/>
       </c>
-      <c r="H28" t="n">
+      <c r="H28" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="3">
         <f>F28/H28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="n">
+        <v>46241</v>
+      </c>
+      <c r="E29" t="n">
+        <v>637851.66</v>
+      </c>
+      <c r="F29">
+        <f>E29-E28</f>
+        <v/>
+      </c>
+      <c r="G29">
+        <f>F29/E28</f>
+        <v/>
+      </c>
+      <c r="H29" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I29">
+        <f>F29/H29</f>
         <v/>
       </c>
     </row>
@@ -2705,7 +2781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -3744,17 +3820,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -3762,22 +3838,60 @@
       <c r="D28" s="23" t="n">
         <v>46240</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="3" t="n">
         <v>2570538.77</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="3">
         <f>E28-E27</f>
         <v/>
       </c>
-      <c r="G28">
+      <c r="G28" s="3">
         <f>F28/E27</f>
         <v/>
       </c>
-      <c r="H28" t="n">
+      <c r="H28" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="3">
         <f>F28/H28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="n">
+        <v>46241</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2512848.77</v>
+      </c>
+      <c r="F29">
+        <f>E29-E28</f>
+        <v/>
+      </c>
+      <c r="G29">
+        <f>F29/E28</f>
+        <v/>
+      </c>
+      <c r="H29" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I29">
+        <f>F29/H29</f>
         <v/>
       </c>
     </row>
@@ -3880,11 +3994,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续3日减持</t>
+          <t>连续4日减持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-3+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-4+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -3921,11 +4035,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续3日减持</t>
+          <t>连续4日减持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-3+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-4+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -3962,11 +4076,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续3日减持</t>
+          <t>连续4日减持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-3+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-4+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4003,11 +4117,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续5日减持</t>
+          <t>连续6日减持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-5+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-6+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4022,7 +4136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5049,17 +5163,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -5067,22 +5181,60 @@
       <c r="D28" s="23" t="n">
         <v>46240</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="3" t="n">
         <v>1876845.49</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="3">
         <f>E28-E27</f>
         <v/>
       </c>
-      <c r="G28">
+      <c r="G28" s="3">
         <f>F28/E27</f>
         <v/>
       </c>
-      <c r="H28" t="n">
+      <c r="H28" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="3">
         <f>F28/H28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="n">
+        <v>46241</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1833945.49</v>
+      </c>
+      <c r="F29">
+        <f>E29-E28</f>
+        <v/>
+      </c>
+      <c r="G29">
+        <f>F29/E28</f>
+        <v/>
+      </c>
+      <c r="H29" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I29">
+        <f>F29/H29</f>
         <v/>
       </c>
     </row>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -1620,17 +1620,17 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -1638,22 +1638,60 @@
       <c r="D29" s="23" t="n">
         <v>46241</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="3" t="n">
         <v>689466.6800000001</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="3">
         <f>E29-E28</f>
         <v/>
       </c>
-      <c r="G29">
+      <c r="G29" s="3">
         <f>F29/E28</f>
         <v/>
       </c>
-      <c r="H29" t="n">
+      <c r="H29" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="3">
         <f>F29/H29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E30" t="n">
+        <v>677856.6800000001</v>
+      </c>
+      <c r="F30">
+        <f>E30-E29</f>
+        <v/>
+      </c>
+      <c r="G30">
+        <f>F30/E29</f>
+        <v/>
+      </c>
+      <c r="H30" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I30">
+        <f>F30/H30</f>
         <v/>
       </c>
     </row>
@@ -1668,7 +1706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2733,17 +2771,17 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -2751,22 +2789,60 @@
       <c r="D29" s="23" t="n">
         <v>46241</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="3" t="n">
         <v>637851.66</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="3">
         <f>E29-E28</f>
         <v/>
       </c>
-      <c r="G29">
+      <c r="G29" s="3">
         <f>F29/E28</f>
         <v/>
       </c>
-      <c r="H29" t="n">
+      <c r="H29" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="3">
         <f>F29/H29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E30" t="n">
+        <v>633531.66</v>
+      </c>
+      <c r="F30">
+        <f>E30-E29</f>
+        <v/>
+      </c>
+      <c r="G30">
+        <f>F30/E29</f>
+        <v/>
+      </c>
+      <c r="H30" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I30">
+        <f>F30/H30</f>
         <v/>
       </c>
     </row>
@@ -2781,7 +2857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -3858,17 +3934,17 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -3876,22 +3952,60 @@
       <c r="D29" s="23" t="n">
         <v>46241</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="3" t="n">
         <v>2512848.77</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="3">
         <f>E29-E28</f>
         <v/>
       </c>
-      <c r="G29">
+      <c r="G29" s="3">
         <f>F29/E28</f>
         <v/>
       </c>
-      <c r="H29" t="n">
+      <c r="H29" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="3">
         <f>F29/H29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2486118.77</v>
+      </c>
+      <c r="F30">
+        <f>E30-E29</f>
+        <v/>
+      </c>
+      <c r="G30">
+        <f>F30/E29</f>
+        <v/>
+      </c>
+      <c r="H30" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I30">
+        <f>F30/H30</f>
         <v/>
       </c>
     </row>
@@ -3994,11 +4108,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续4日减持</t>
+          <t>连续5日减持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-4+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-5+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4035,11 +4149,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续4日减持</t>
+          <t>连续5日减持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-4+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-5+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4076,11 +4190,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续4日减持</t>
+          <t>连续5日减持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-4+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-5+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4117,11 +4231,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续6日减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-6+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-1+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4136,7 +4250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5201,17 +5315,17 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -5219,22 +5333,60 @@
       <c r="D29" s="23" t="n">
         <v>46241</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="3" t="n">
         <v>1833945.49</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="3">
         <f>E29-E28</f>
         <v/>
       </c>
-      <c r="G29">
+      <c r="G29" s="3">
         <f>F29/E28</f>
         <v/>
       </c>
-      <c r="H29" t="n">
+      <c r="H29" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="3">
         <f>F29/H29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1857445.49</v>
+      </c>
+      <c r="F30">
+        <f>E30-E29</f>
+        <v/>
+      </c>
+      <c r="G30">
+        <f>F30/E29</f>
+        <v/>
+      </c>
+      <c r="H30" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I30">
+        <f>F30/H30</f>
         <v/>
       </c>
     </row>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -1658,17 +1658,17 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -1676,22 +1676,60 @@
       <c r="D30" s="23" t="n">
         <v>46244</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="3" t="n">
         <v>677856.6800000001</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="3">
         <f>E30-E29</f>
         <v/>
       </c>
-      <c r="G30">
+      <c r="G30" s="3">
         <f>F30/E29</f>
         <v/>
       </c>
-      <c r="H30" t="n">
+      <c r="H30" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="3">
         <f>F30/H30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E31" t="n">
+        <v>714666.6800000001</v>
+      </c>
+      <c r="F31">
+        <f>E31-E30</f>
+        <v/>
+      </c>
+      <c r="G31">
+        <f>F31/E30</f>
+        <v/>
+      </c>
+      <c r="H31" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I31">
+        <f>F31/H31</f>
         <v/>
       </c>
     </row>
@@ -1706,7 +1744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2809,17 +2847,17 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -2827,22 +2865,60 @@
       <c r="D30" s="23" t="n">
         <v>46244</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="3" t="n">
         <v>633531.66</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="3">
         <f>E30-E29</f>
         <v/>
       </c>
-      <c r="G30">
+      <c r="G30" s="3">
         <f>F30/E29</f>
         <v/>
       </c>
-      <c r="H30" t="n">
+      <c r="H30" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="3">
         <f>F30/H30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E31" t="n">
+        <v>633981.66</v>
+      </c>
+      <c r="F31">
+        <f>E31-E30</f>
+        <v/>
+      </c>
+      <c r="G31">
+        <f>F31/E30</f>
+        <v/>
+      </c>
+      <c r="H31" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I31">
+        <f>F31/H31</f>
         <v/>
       </c>
     </row>
@@ -2857,7 +2933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -3972,17 +4048,17 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -3990,22 +4066,60 @@
       <c r="D30" s="23" t="n">
         <v>46244</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="3" t="n">
         <v>2486118.77</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="3">
         <f>E30-E29</f>
         <v/>
       </c>
-      <c r="G30">
+      <c r="G30" s="3">
         <f>F30/E29</f>
         <v/>
       </c>
-      <c r="H30" t="n">
+      <c r="H30" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="3">
         <f>F30/H30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2482428.77</v>
+      </c>
+      <c r="F31">
+        <f>E31-E30</f>
+        <v/>
+      </c>
+      <c r="G31">
+        <f>F31/E30</f>
+        <v/>
+      </c>
+      <c r="H31" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I31">
+        <f>F31/H31</f>
         <v/>
       </c>
     </row>
@@ -4108,11 +4222,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续5日减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-5+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-1+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4149,11 +4263,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续5日减持</t>
+          <t>连续6日减持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-5+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-6+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4190,11 +4304,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续5日减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-5+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4231,7 +4345,7 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I5" s="13">
@@ -4250,7 +4364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5353,17 +5467,17 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -5371,22 +5485,60 @@
       <c r="D30" s="23" t="n">
         <v>46244</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="3" t="n">
         <v>1857445.49</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="3">
         <f>E30-E29</f>
         <v/>
       </c>
-      <c r="G30">
+      <c r="G30" s="3">
         <f>F30/E29</f>
         <v/>
       </c>
-      <c r="H30" t="n">
+      <c r="H30" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="3">
         <f>F30/H30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1816745.49</v>
+      </c>
+      <c r="F31">
+        <f>E31-E30</f>
+        <v/>
+      </c>
+      <c r="G31">
+        <f>F31/E30</f>
+        <v/>
+      </c>
+      <c r="H31" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I31">
+        <f>F31/H31</f>
         <v/>
       </c>
     </row>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -1696,17 +1696,17 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -1714,22 +1714,60 @@
       <c r="D31" s="23" t="n">
         <v>46245</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="3" t="n">
         <v>714666.6800000001</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="3">
         <f>E31-E30</f>
         <v/>
       </c>
-      <c r="G31">
+      <c r="G31" s="3">
         <f>F31/E30</f>
         <v/>
       </c>
-      <c r="H31" t="n">
+      <c r="H31" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="3">
         <f>F31/H31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E32" t="n">
+        <v>700446.6800000001</v>
+      </c>
+      <c r="F32">
+        <f>E32-E31</f>
+        <v/>
+      </c>
+      <c r="G32">
+        <f>F32/E31</f>
+        <v/>
+      </c>
+      <c r="H32" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I32">
+        <f>F32/H32</f>
         <v/>
       </c>
     </row>
@@ -1744,7 +1782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2885,17 +2923,17 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -2903,22 +2941,60 @@
       <c r="D31" s="23" t="n">
         <v>46245</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="3" t="n">
         <v>633981.66</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="3">
         <f>E31-E30</f>
         <v/>
       </c>
-      <c r="G31">
+      <c r="G31" s="3">
         <f>F31/E30</f>
         <v/>
       </c>
-      <c r="H31" t="n">
+      <c r="H31" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="3">
         <f>F31/H31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E32" t="n">
+        <v>628491.66</v>
+      </c>
+      <c r="F32">
+        <f>E32-E31</f>
+        <v/>
+      </c>
+      <c r="G32">
+        <f>F32/E31</f>
+        <v/>
+      </c>
+      <c r="H32" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I32">
+        <f>F32/H32</f>
         <v/>
       </c>
     </row>
@@ -2933,7 +3009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -4086,17 +4162,17 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -4104,22 +4180,60 @@
       <c r="D31" s="23" t="n">
         <v>46245</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="3" t="n">
         <v>2482428.77</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="3">
         <f>E31-E30</f>
         <v/>
       </c>
-      <c r="G31">
+      <c r="G31" s="3">
         <f>F31/E30</f>
         <v/>
       </c>
-      <c r="H31" t="n">
+      <c r="H31" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="3">
         <f>F31/H31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2416818.77</v>
+      </c>
+      <c r="F32">
+        <f>E32-E31</f>
+        <v/>
+      </c>
+      <c r="G32">
+        <f>F32/E31</f>
+        <v/>
+      </c>
+      <c r="H32" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I32">
+        <f>F32/H32</f>
         <v/>
       </c>
     </row>
@@ -4222,7 +4336,7 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I2" s="13">
@@ -4263,11 +4377,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续6日减持</t>
+          <t>连续7日减持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-6+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-7+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4304,7 +4418,7 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I4" s="13">
@@ -4345,11 +4459,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>连续2日减持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-1+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-2+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4364,7 +4478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5505,17 +5619,17 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -5523,22 +5637,60 @@
       <c r="D31" s="23" t="n">
         <v>46245</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="3" t="n">
         <v>1816745.49</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="3">
         <f>E31-E30</f>
         <v/>
       </c>
-      <c r="G31">
+      <c r="G31" s="3">
         <f>F31/E30</f>
         <v/>
       </c>
-      <c r="H31" t="n">
+      <c r="H31" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="3">
         <f>F31/H31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1798145.49</v>
+      </c>
+      <c r="F32">
+        <f>E32-E31</f>
+        <v/>
+      </c>
+      <c r="G32">
+        <f>F32/E31</f>
+        <v/>
+      </c>
+      <c r="H32" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I32">
+        <f>F32/H32</f>
         <v/>
       </c>
     </row>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -1734,17 +1734,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -1752,21 +1752,21 @@
       <c r="D32" s="23" t="n">
         <v>46246</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="3" t="n">
         <v>700446.6800000001</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="3">
         <f>E32-E31</f>
         <v/>
       </c>
-      <c r="G32">
+      <c r="G32" s="3">
         <f>F32/E31</f>
         <v/>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="3">
         <f>F32/H32</f>
         <v/>
       </c>
@@ -1782,7 +1782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2961,17 +2961,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -2979,22 +2979,60 @@
       <c r="D32" s="23" t="n">
         <v>46246</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="3" t="n">
         <v>628491.66</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="3">
         <f>E32-E31</f>
         <v/>
       </c>
-      <c r="G32">
+      <c r="G32" s="3">
         <f>F32/E31</f>
         <v/>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="3">
         <f>F32/H32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E33" t="n">
+        <v>623541.66</v>
+      </c>
+      <c r="F33">
+        <f>E33-E32</f>
+        <v/>
+      </c>
+      <c r="G33">
+        <f>F33/E32</f>
+        <v/>
+      </c>
+      <c r="H33" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I33">
+        <f>F33/H33</f>
         <v/>
       </c>
     </row>
@@ -4200,17 +4238,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -4218,21 +4256,21 @@
       <c r="D32" s="23" t="n">
         <v>46246</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="3" t="n">
         <v>2416818.77</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="3">
         <f>E32-E31</f>
         <v/>
       </c>
-      <c r="G32">
+      <c r="G32" s="3">
         <f>F32/E31</f>
         <v/>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="3">
         <f>F32/H32</f>
         <v/>
       </c>
@@ -4418,11 +4456,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>连续2日减持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4459,11 +4497,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续2日减持</t>
+          <t>连续3日减持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-2+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-3+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4478,7 +4516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5657,17 +5695,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -5675,22 +5713,60 @@
       <c r="D32" s="23" t="n">
         <v>46246</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="3" t="n">
         <v>1798145.49</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="3">
         <f>E32-E31</f>
         <v/>
       </c>
-      <c r="G32">
+      <c r="G32" s="3">
         <f>F32/E31</f>
         <v/>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="3">
         <f>F32/H32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1766045.49</v>
+      </c>
+      <c r="F33">
+        <f>E33-E32</f>
+        <v/>
+      </c>
+      <c r="G33">
+        <f>F33/E32</f>
+        <v/>
+      </c>
+      <c r="H33" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I33">
+        <f>F33/H33</f>
         <v/>
       </c>
     </row>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -1782,7 +1782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2999,17 +2999,17 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -3017,22 +3017,60 @@
       <c r="D33" s="23" t="n">
         <v>46247</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="3" t="n">
         <v>623541.66</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="3">
         <f>E33-E32</f>
         <v/>
       </c>
-      <c r="G33">
+      <c r="G33" s="3">
         <f>F33/E32</f>
         <v/>
       </c>
-      <c r="H33" t="n">
+      <c r="H33" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="3">
         <f>F33/H33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E34" t="n">
+        <v>622731.66</v>
+      </c>
+      <c r="F34">
+        <f>E34-E33</f>
+        <v/>
+      </c>
+      <c r="G34">
+        <f>F34/E33</f>
+        <v/>
+      </c>
+      <c r="H34" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I34">
+        <f>F34/H34</f>
         <v/>
       </c>
     </row>
@@ -4456,11 +4494,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续2日减持</t>
+          <t>连续3日减持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-3+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4497,11 +4535,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续3日减持</t>
+          <t>连续4日减持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-3+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-4+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4516,7 +4554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5733,17 +5771,17 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -5751,22 +5789,60 @@
       <c r="D33" s="23" t="n">
         <v>46247</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="3" t="n">
         <v>1766045.49</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="3">
         <f>E33-E32</f>
         <v/>
       </c>
-      <c r="G33">
+      <c r="G33" s="3">
         <f>F33/E32</f>
         <v/>
       </c>
-      <c r="H33" t="n">
+      <c r="H33" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="3">
         <f>F33/H33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1746045.49</v>
+      </c>
+      <c r="F34">
+        <f>E34-E33</f>
+        <v/>
+      </c>
+      <c r="G34">
+        <f>F34/E33</f>
+        <v/>
+      </c>
+      <c r="H34" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I34">
+        <f>F34/H34</f>
         <v/>
       </c>
     </row>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -1768,6 +1768,44 @@
       </c>
       <c r="I32" s="3">
         <f>F32/H32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="n">
+        <v>46251</v>
+      </c>
+      <c r="E33" t="n">
+        <v>691986.6800000001</v>
+      </c>
+      <c r="F33">
+        <f>E33-E32</f>
+        <v/>
+      </c>
+      <c r="G33">
+        <f>F33/E32</f>
+        <v/>
+      </c>
+      <c r="H33" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I33">
+        <f>F33/H33</f>
         <v/>
       </c>
     </row>
@@ -1782,7 +1820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3037,17 +3075,17 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -3055,22 +3093,60 @@
       <c r="D34" s="23" t="n">
         <v>46248</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="3" t="n">
         <v>622731.66</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="3">
         <f>E34-E33</f>
         <v/>
       </c>
-      <c r="G34">
+      <c r="G34" s="3">
         <f>F34/E33</f>
         <v/>
       </c>
-      <c r="H34" t="n">
+      <c r="H34" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="3">
         <f>F34/H34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="n">
+        <v>46251</v>
+      </c>
+      <c r="E35" t="n">
+        <v>617241.66</v>
+      </c>
+      <c r="F35">
+        <f>E35-E34</f>
+        <v/>
+      </c>
+      <c r="G35">
+        <f>F35/E34</f>
+        <v/>
+      </c>
+      <c r="H35" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I35">
+        <f>F35/H35</f>
         <v/>
       </c>
     </row>
@@ -3085,7 +3161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -4310,6 +4386,44 @@
       </c>
       <c r="I32" s="3">
         <f>F32/H32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="n">
+        <v>46251</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2304408.77</v>
+      </c>
+      <c r="F33">
+        <f>E33-E32</f>
+        <v/>
+      </c>
+      <c r="G33">
+        <f>F33/E32</f>
+        <v/>
+      </c>
+      <c r="H33" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I33">
+        <f>F33/H33</f>
         <v/>
       </c>
     </row>
@@ -4412,11 +4526,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>连续2日减持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-1+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-2+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4453,11 +4567,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续7日减持</t>
+          <t>连续8日减持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-7+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-8+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4494,11 +4608,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续3日减持</t>
+          <t>连续4日减持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-3+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-4+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4535,11 +4649,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续4日减持</t>
+          <t>连续5日减持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-4+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-5+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4554,7 +4668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5809,17 +5923,17 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -5827,22 +5941,60 @@
       <c r="D34" s="23" t="n">
         <v>46248</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="3" t="n">
         <v>1746045.49</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="3">
         <f>E34-E33</f>
         <v/>
       </c>
-      <c r="G34">
+      <c r="G34" s="3">
         <f>F34/E33</f>
         <v/>
       </c>
-      <c r="H34" t="n">
+      <c r="H34" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="3">
         <f>F34/H34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="n">
+        <v>46251</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1711445.49</v>
+      </c>
+      <c r="F35">
+        <f>E35-E34</f>
+        <v/>
+      </c>
+      <c r="G35">
+        <f>F35/E34</f>
+        <v/>
+      </c>
+      <c r="H35" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I35">
+        <f>F35/H35</f>
         <v/>
       </c>
     </row>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -1772,17 +1772,17 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -1790,21 +1790,21 @@
       <c r="D33" s="23" t="n">
         <v>46251</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="3" t="n">
         <v>691986.6800000001</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="3">
         <f>E33-E32</f>
         <v/>
       </c>
-      <c r="G33">
+      <c r="G33" s="3">
         <f>F33/E32</f>
         <v/>
       </c>
-      <c r="H33" t="n">
+      <c r="H33" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="3">
         <f>F33/H33</f>
         <v/>
       </c>
@@ -1820,7 +1820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3113,17 +3113,17 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -3131,22 +3131,60 @@
       <c r="D35" s="23" t="n">
         <v>46251</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="3" t="n">
         <v>617241.66</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="3">
         <f>E35-E34</f>
         <v/>
       </c>
-      <c r="G35">
+      <c r="G35" s="3">
         <f>F35/E34</f>
         <v/>
       </c>
-      <c r="H35" t="n">
+      <c r="H35" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I35">
+      <c r="I35" s="3">
         <f>F35/H35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E36" t="n">
+        <v>613281.66</v>
+      </c>
+      <c r="F36">
+        <f>E36-E35</f>
+        <v/>
+      </c>
+      <c r="G36">
+        <f>F36/E35</f>
+        <v/>
+      </c>
+      <c r="H36" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I36">
+        <f>F36/H36</f>
         <v/>
       </c>
     </row>
@@ -4390,17 +4428,17 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -4408,21 +4446,21 @@
       <c r="D33" s="23" t="n">
         <v>46251</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="3" t="n">
         <v>2304408.77</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="3">
         <f>E33-E32</f>
         <v/>
       </c>
-      <c r="G33">
+      <c r="G33" s="3">
         <f>F33/E32</f>
         <v/>
       </c>
-      <c r="H33" t="n">
+      <c r="H33" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="3">
         <f>F33/H33</f>
         <v/>
       </c>
@@ -4608,11 +4646,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续4日减持</t>
+          <t>连续5日减持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-4+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-5+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4649,11 +4687,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续5日减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-5+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-1+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4668,7 +4706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5961,17 +5999,17 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -5979,22 +6017,60 @@
       <c r="D35" s="23" t="n">
         <v>46251</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="3" t="n">
         <v>1711445.49</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="3">
         <f>E35-E34</f>
         <v/>
       </c>
-      <c r="G35">
+      <c r="G35" s="3">
         <f>F35/E34</f>
         <v/>
       </c>
-      <c r="H35" t="n">
+      <c r="H35" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I35">
+      <c r="I35" s="3">
         <f>F35/H35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1719145.49</v>
+      </c>
+      <c r="F36">
+        <f>E36-E35</f>
+        <v/>
+      </c>
+      <c r="G36">
+        <f>F36/E35</f>
+        <v/>
+      </c>
+      <c r="H36" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I36">
+        <f>F36/H36</f>
         <v/>
       </c>
     </row>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -1806,6 +1806,44 @@
       </c>
       <c r="I33" s="3">
         <f>F33/H33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E34" t="n">
+        <v>694056.6800000001</v>
+      </c>
+      <c r="F34">
+        <f>E34-E33</f>
+        <v/>
+      </c>
+      <c r="G34">
+        <f>F34/E33</f>
+        <v/>
+      </c>
+      <c r="H34" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I34">
+        <f>F34/H34</f>
         <v/>
       </c>
     </row>
@@ -1820,7 +1858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3151,17 +3189,17 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -3169,22 +3207,60 @@
       <c r="D36" s="23" t="n">
         <v>46252</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="3" t="n">
         <v>613281.66</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="3">
         <f>E36-E35</f>
         <v/>
       </c>
-      <c r="G36">
+      <c r="G36" s="3">
         <f>F36/E35</f>
         <v/>
       </c>
-      <c r="H36" t="n">
+      <c r="H36" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I36">
+      <c r="I36" s="3">
         <f>F36/H36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E37" t="n">
+        <v>626601.66</v>
+      </c>
+      <c r="F37">
+        <f>E37-E36</f>
+        <v/>
+      </c>
+      <c r="G37">
+        <f>F37/E36</f>
+        <v/>
+      </c>
+      <c r="H37" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I37">
+        <f>F37/H37</f>
         <v/>
       </c>
     </row>
@@ -3199,7 +3275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -4462,6 +4538,44 @@
       </c>
       <c r="I33" s="3">
         <f>F33/H33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2385858.77</v>
+      </c>
+      <c r="F34">
+        <f>E34-E33</f>
+        <v/>
+      </c>
+      <c r="G34">
+        <f>F34/E33</f>
+        <v/>
+      </c>
+      <c r="H34" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I34">
+        <f>F34/H34</f>
         <v/>
       </c>
     </row>
@@ -4564,11 +4678,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续2日减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-2+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-1+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4605,11 +4719,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续8日减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-8+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-1+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4646,11 +4760,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续5日减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-5+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4687,11 +4801,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>连续2日增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-1+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-2+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4706,7 +4820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6037,17 +6151,17 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -6055,22 +6169,60 @@
       <c r="D36" s="23" t="n">
         <v>46252</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="3" t="n">
         <v>1719145.49</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="3">
         <f>E36-E35</f>
         <v/>
       </c>
-      <c r="G36">
+      <c r="G36" s="3">
         <f>F36/E35</f>
         <v/>
       </c>
-      <c r="H36" t="n">
+      <c r="H36" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I36">
+      <c r="I36" s="3">
         <f>F36/H36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1841045.49</v>
+      </c>
+      <c r="F37">
+        <f>E37-E36</f>
+        <v/>
+      </c>
+      <c r="G37">
+        <f>F37/E36</f>
+        <v/>
+      </c>
+      <c r="H37" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I37">
+        <f>F37/H37</f>
         <v/>
       </c>
     </row>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -1810,17 +1810,17 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -1828,22 +1828,60 @@
       <c r="D34" s="23" t="n">
         <v>46253</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="3" t="n">
         <v>694056.6800000001</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="3">
         <f>E34-E33</f>
         <v/>
       </c>
-      <c r="G34">
+      <c r="G34" s="3">
         <f>F34/E33</f>
         <v/>
       </c>
-      <c r="H34" t="n">
+      <c r="H34" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="3">
         <f>F34/H34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E35" t="n">
+        <v>729246.6800000001</v>
+      </c>
+      <c r="F35">
+        <f>E35-E34</f>
+        <v/>
+      </c>
+      <c r="G35">
+        <f>F35/E34</f>
+        <v/>
+      </c>
+      <c r="H35" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I35">
+        <f>F35/H35</f>
         <v/>
       </c>
     </row>
@@ -1858,7 +1896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3227,17 +3265,17 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -3245,22 +3283,60 @@
       <c r="D37" s="23" t="n">
         <v>46253</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="3" t="n">
         <v>626601.66</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="3">
         <f>E37-E36</f>
         <v/>
       </c>
-      <c r="G37">
+      <c r="G37" s="3">
         <f>F37/E36</f>
         <v/>
       </c>
-      <c r="H37" t="n">
+      <c r="H37" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="3">
         <f>F37/H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E38" t="n">
+        <v>627141.66</v>
+      </c>
+      <c r="F38">
+        <f>E38-E37</f>
+        <v/>
+      </c>
+      <c r="G38">
+        <f>F38/E37</f>
+        <v/>
+      </c>
+      <c r="H38" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I38">
+        <f>F38/H38</f>
         <v/>
       </c>
     </row>
@@ -3275,7 +3351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -4542,17 +4618,17 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -4560,22 +4636,60 @@
       <c r="D34" s="23" t="n">
         <v>46253</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="3" t="n">
         <v>2385858.77</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="3">
         <f>E34-E33</f>
         <v/>
       </c>
-      <c r="G34">
+      <c r="G34" s="3">
         <f>F34/E33</f>
         <v/>
       </c>
-      <c r="H34" t="n">
+      <c r="H34" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="3">
         <f>F34/H34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2374338.77</v>
+      </c>
+      <c r="F35">
+        <f>E35-E34</f>
+        <v/>
+      </c>
+      <c r="G35">
+        <f>F35/E34</f>
+        <v/>
+      </c>
+      <c r="H35" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I35">
+        <f>F35/H35</f>
         <v/>
       </c>
     </row>
@@ -4678,11 +4792,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>连续2日增持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-1+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-2+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4719,7 +4833,7 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I3" s="13">
@@ -4760,11 +4874,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>连续2日增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4801,11 +4915,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续2日增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-2+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-1+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4820,7 +4934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6189,17 +6303,17 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -6207,22 +6321,60 @@
       <c r="D37" s="23" t="n">
         <v>46253</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="3" t="n">
         <v>1841045.49</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="3">
         <f>E37-E36</f>
         <v/>
       </c>
-      <c r="G37">
+      <c r="G37" s="3">
         <f>F37/E36</f>
         <v/>
       </c>
-      <c r="H37" t="n">
+      <c r="H37" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="3">
         <f>F37/H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1816045.49</v>
+      </c>
+      <c r="F38">
+        <f>E38-E37</f>
+        <v/>
+      </c>
+      <c r="G38">
+        <f>F38/E37</f>
+        <v/>
+      </c>
+      <c r="H38" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I38">
+        <f>F38/H38</f>
         <v/>
       </c>
     </row>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -1848,17 +1848,17 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -1866,21 +1866,21 @@
       <c r="D35" s="23" t="n">
         <v>46254</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="3" t="n">
         <v>729246.6800000001</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="3">
         <f>E35-E34</f>
         <v/>
       </c>
-      <c r="G35">
+      <c r="G35" s="3">
         <f>F35/E34</f>
         <v/>
       </c>
-      <c r="H35" t="n">
+      <c r="H35" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I35">
+      <c r="I35" s="3">
         <f>F35/H35</f>
         <v/>
       </c>
@@ -1896,7 +1896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3303,17 +3303,17 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -3321,22 +3321,60 @@
       <c r="D38" s="23" t="n">
         <v>46254</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="3" t="n">
         <v>627141.66</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="3">
         <f>E38-E37</f>
         <v/>
       </c>
-      <c r="G38">
+      <c r="G38" s="3">
         <f>F38/E37</f>
         <v/>
       </c>
-      <c r="H38" t="n">
+      <c r="H38" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I38">
+      <c r="I38" s="3">
         <f>F38/H38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D39" s="23" t="n">
+        <v>46255</v>
+      </c>
+      <c r="E39" t="n">
+        <v>622101.66</v>
+      </c>
+      <c r="F39">
+        <f>E39-E38</f>
+        <v/>
+      </c>
+      <c r="G39">
+        <f>F39/E38</f>
+        <v/>
+      </c>
+      <c r="H39" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I39">
+        <f>F39/H39</f>
         <v/>
       </c>
     </row>
@@ -4656,17 +4694,17 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -4674,21 +4712,21 @@
       <c r="D35" s="23" t="n">
         <v>46254</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="3" t="n">
         <v>2374338.77</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="3">
         <f>E35-E34</f>
         <v/>
       </c>
-      <c r="G35">
+      <c r="G35" s="3">
         <f>F35/E34</f>
         <v/>
       </c>
-      <c r="H35" t="n">
+      <c r="H35" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I35">
+      <c r="I35" s="3">
         <f>F35/H35</f>
         <v/>
       </c>
@@ -4874,11 +4912,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续2日增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4915,11 +4953,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>连续2日减持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-1+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-2+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4934,7 +4972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6341,17 +6379,17 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -6359,22 +6397,60 @@
       <c r="D38" s="23" t="n">
         <v>46254</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="3" t="n">
         <v>1816045.49</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="3">
         <f>E38-E37</f>
         <v/>
       </c>
-      <c r="G38">
+      <c r="G38" s="3">
         <f>F38/E37</f>
         <v/>
       </c>
-      <c r="H38" t="n">
+      <c r="H38" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I38">
+      <c r="I38" s="3">
         <f>F38/H38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D39" s="23" t="n">
+        <v>46255</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1774545.49</v>
+      </c>
+      <c r="F39">
+        <f>E39-E38</f>
+        <v/>
+      </c>
+      <c r="G39">
+        <f>F39/E38</f>
+        <v/>
+      </c>
+      <c r="H39" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I39">
+        <f>F39/H39</f>
         <v/>
       </c>
     </row>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -1882,6 +1882,44 @@
       </c>
       <c r="I35" s="3">
         <f>F35/H35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="n">
+        <v>46258</v>
+      </c>
+      <c r="E36" t="n">
+        <v>752106.6800000001</v>
+      </c>
+      <c r="F36">
+        <f>E36-E35</f>
+        <v/>
+      </c>
+      <c r="G36">
+        <f>F36/E35</f>
+        <v/>
+      </c>
+      <c r="H36" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I36">
+        <f>F36/H36</f>
         <v/>
       </c>
     </row>
@@ -1896,7 +1934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3341,17 +3379,17 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -3359,22 +3397,60 @@
       <c r="D39" s="23" t="n">
         <v>46255</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="3" t="n">
         <v>622101.66</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="3">
         <f>E39-E38</f>
         <v/>
       </c>
-      <c r="G39">
+      <c r="G39" s="3">
         <f>F39/E38</f>
         <v/>
       </c>
-      <c r="H39" t="n">
+      <c r="H39" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="3">
         <f>F39/H39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="n">
+        <v>46258</v>
+      </c>
+      <c r="E40" t="n">
+        <v>627861.66</v>
+      </c>
+      <c r="F40">
+        <f>E40-E39</f>
+        <v/>
+      </c>
+      <c r="G40">
+        <f>F40/E39</f>
+        <v/>
+      </c>
+      <c r="H40" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I40">
+        <f>F40/H40</f>
         <v/>
       </c>
     </row>
@@ -3389,7 +3465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -4728,6 +4804,44 @@
       </c>
       <c r="I35" s="3">
         <f>F35/H35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="n">
+        <v>46258</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2380908.77</v>
+      </c>
+      <c r="F36">
+        <f>E36-E35</f>
+        <v/>
+      </c>
+      <c r="G36">
+        <f>F36/E35</f>
+        <v/>
+      </c>
+      <c r="H36" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I36">
+        <f>F36/H36</f>
         <v/>
       </c>
     </row>
@@ -4830,11 +4944,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续2日增持</t>
+          <t>连续3日增持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-2+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-3+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4871,7 +4985,7 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I3" s="13">
@@ -4912,7 +5026,7 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I4" s="13">
@@ -4953,11 +5067,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续2日减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-2+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-1+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4972,7 +5086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6417,17 +6531,17 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -6435,22 +6549,60 @@
       <c r="D39" s="23" t="n">
         <v>46255</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="3" t="n">
         <v>1774545.49</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="3">
         <f>E39-E38</f>
         <v/>
       </c>
-      <c r="G39">
+      <c r="G39" s="3">
         <f>F39/E38</f>
         <v/>
       </c>
-      <c r="H39" t="n">
+      <c r="H39" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="3">
         <f>F39/H39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="n">
+        <v>46258</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1831645.49</v>
+      </c>
+      <c r="F40">
+        <f>E40-E39</f>
+        <v/>
+      </c>
+      <c r="G40">
+        <f>F40/E39</f>
+        <v/>
+      </c>
+      <c r="H40" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I40">
+        <f>F40/H40</f>
         <v/>
       </c>
     </row>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -1886,17 +1886,17 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -1904,22 +1904,60 @@
       <c r="D36" s="23" t="n">
         <v>46258</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="3" t="n">
         <v>752106.6800000001</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="3">
         <f>E36-E35</f>
         <v/>
       </c>
-      <c r="G36">
+      <c r="G36" s="3">
         <f>F36/E35</f>
         <v/>
       </c>
-      <c r="H36" t="n">
+      <c r="H36" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I36">
+      <c r="I36" s="3">
         <f>F36/H36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E37" t="n">
+        <v>763356.6800000001</v>
+      </c>
+      <c r="F37">
+        <f>E37-E36</f>
+        <v/>
+      </c>
+      <c r="G37">
+        <f>F37/E36</f>
+        <v/>
+      </c>
+      <c r="H37" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I37">
+        <f>F37/H37</f>
         <v/>
       </c>
     </row>
@@ -1934,7 +1972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3417,17 +3455,17 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -3435,22 +3473,60 @@
       <c r="D40" s="23" t="n">
         <v>46258</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="3" t="n">
         <v>627861.66</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="3">
         <f>E40-E39</f>
         <v/>
       </c>
-      <c r="G40">
+      <c r="G40" s="3">
         <f>F40/E39</f>
         <v/>
       </c>
-      <c r="H40" t="n">
+      <c r="H40" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="3">
         <f>F40/H40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E41" t="n">
+        <v>630021.66</v>
+      </c>
+      <c r="F41">
+        <f>E41-E40</f>
+        <v/>
+      </c>
+      <c r="G41">
+        <f>F41/E40</f>
+        <v/>
+      </c>
+      <c r="H41" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I41">
+        <f>F41/H41</f>
         <v/>
       </c>
     </row>
@@ -3465,7 +3541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -4808,17 +4884,17 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -4826,22 +4902,60 @@
       <c r="D36" s="23" t="n">
         <v>46258</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="3" t="n">
         <v>2380908.77</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="3">
         <f>E36-E35</f>
         <v/>
       </c>
-      <c r="G36">
+      <c r="G36" s="3">
         <f>F36/E35</f>
         <v/>
       </c>
-      <c r="H36" t="n">
+      <c r="H36" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I36">
+      <c r="I36" s="3">
         <f>F36/H36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2405298.77</v>
+      </c>
+      <c r="F37">
+        <f>E37-E36</f>
+        <v/>
+      </c>
+      <c r="G37">
+        <f>F37/E36</f>
+        <v/>
+      </c>
+      <c r="H37" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I37">
+        <f>F37/H37</f>
         <v/>
       </c>
     </row>
@@ -4944,11 +5058,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续3日增持</t>
+          <t>连续4日增持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-3+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-4+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -4985,11 +5099,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>连续2日增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-1+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-2+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5026,11 +5140,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>连续2日增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5067,11 +5181,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>连续2日增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-1+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-2+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5086,7 +5200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6569,17 +6683,17 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -6587,22 +6701,60 @@
       <c r="D40" s="23" t="n">
         <v>46258</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="3" t="n">
         <v>1831645.49</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="3">
         <f>E40-E39</f>
         <v/>
       </c>
-      <c r="G40">
+      <c r="G40" s="3">
         <f>F40/E39</f>
         <v/>
       </c>
-      <c r="H40" t="n">
+      <c r="H40" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="3">
         <f>F40/H40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1900445.49</v>
+      </c>
+      <c r="F41">
+        <f>E41-E40</f>
+        <v/>
+      </c>
+      <c r="G41">
+        <f>F41/E40</f>
+        <v/>
+      </c>
+      <c r="H41" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I41">
+        <f>F41/H41</f>
         <v/>
       </c>
     </row>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -1924,17 +1924,17 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -1942,22 +1942,60 @@
       <c r="D37" s="23" t="n">
         <v>46259</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="3" t="n">
         <v>763356.6800000001</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="3">
         <f>E37-E36</f>
         <v/>
       </c>
-      <c r="G37">
+      <c r="G37" s="3">
         <f>F37/E36</f>
         <v/>
       </c>
-      <c r="H37" t="n">
+      <c r="H37" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="3">
         <f>F37/H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E38" t="n">
+        <v>724656.6800000001</v>
+      </c>
+      <c r="F38">
+        <f>E38-E37</f>
+        <v/>
+      </c>
+      <c r="G38">
+        <f>F38/E37</f>
+        <v/>
+      </c>
+      <c r="H38" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I38">
+        <f>F38/H38</f>
         <v/>
       </c>
     </row>
@@ -1972,7 +2010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3493,17 +3531,17 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -3511,22 +3549,60 @@
       <c r="D41" s="23" t="n">
         <v>46259</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="3" t="n">
         <v>630021.66</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="3">
         <f>E41-E40</f>
         <v/>
       </c>
-      <c r="G41">
+      <c r="G41" s="3">
         <f>F41/E40</f>
         <v/>
       </c>
-      <c r="H41" t="n">
+      <c r="H41" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I41">
+      <c r="I41" s="3">
         <f>F41/H41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E42" t="n">
+        <v>630381.66</v>
+      </c>
+      <c r="F42">
+        <f>E42-E41</f>
+        <v/>
+      </c>
+      <c r="G42">
+        <f>F42/E41</f>
+        <v/>
+      </c>
+      <c r="H42" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I42">
+        <f>F42/H42</f>
         <v/>
       </c>
     </row>
@@ -3541,7 +3617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -4922,17 +4998,17 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -4940,22 +5016,60 @@
       <c r="D37" s="23" t="n">
         <v>46259</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="3" t="n">
         <v>2405298.77</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="3">
         <f>E37-E36</f>
         <v/>
       </c>
-      <c r="G37">
+      <c r="G37" s="3">
         <f>F37/E36</f>
         <v/>
       </c>
-      <c r="H37" t="n">
+      <c r="H37" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="3">
         <f>F37/H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2385318.77</v>
+      </c>
+      <c r="F38">
+        <f>E38-E37</f>
+        <v/>
+      </c>
+      <c r="G38">
+        <f>F38/E37</f>
+        <v/>
+      </c>
+      <c r="H38" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I38">
+        <f>F38/H38</f>
         <v/>
       </c>
     </row>
@@ -5058,11 +5172,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续4日增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-4+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-1+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5099,11 +5213,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续2日增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-2+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-1+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5140,11 +5254,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续2日增持</t>
+          <t>连续3日增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-3+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5181,11 +5295,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续2日增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-2+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-1+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5200,7 +5314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6721,17 +6835,17 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -6739,22 +6853,60 @@
       <c r="D41" s="23" t="n">
         <v>46259</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="3" t="n">
         <v>1900445.49</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="3">
         <f>E41-E40</f>
         <v/>
       </c>
-      <c r="G41">
+      <c r="G41" s="3">
         <f>F41/E40</f>
         <v/>
       </c>
-      <c r="H41" t="n">
+      <c r="H41" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I41">
+      <c r="I41" s="3">
         <f>F41/H41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1872245.49</v>
+      </c>
+      <c r="F42">
+        <f>E42-E41</f>
+        <v/>
+      </c>
+      <c r="G42">
+        <f>F42/E41</f>
+        <v/>
+      </c>
+      <c r="H42" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I42">
+        <f>F42/H42</f>
         <v/>
       </c>
     </row>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -1962,17 +1962,17 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -1980,21 +1980,21 @@
       <c r="D38" s="23" t="n">
         <v>46260</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="3" t="n">
         <v>724656.6800000001</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="3">
         <f>E38-E37</f>
         <v/>
       </c>
-      <c r="G38">
+      <c r="G38" s="3">
         <f>F38/E37</f>
         <v/>
       </c>
-      <c r="H38" t="n">
+      <c r="H38" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I38">
+      <c r="I38" s="3">
         <f>F38/H38</f>
         <v/>
       </c>
@@ -2010,7 +2010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3569,17 +3569,17 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -3587,22 +3587,60 @@
       <c r="D42" s="23" t="n">
         <v>46260</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="3" t="n">
         <v>630381.66</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="3">
         <f>E42-E41</f>
         <v/>
       </c>
-      <c r="G42">
+      <c r="G42" s="3">
         <f>F42/E41</f>
         <v/>
       </c>
-      <c r="H42" t="n">
+      <c r="H42" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="3">
         <f>F42/H42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E43" t="n">
+        <v>628491.66</v>
+      </c>
+      <c r="F43">
+        <f>E43-E42</f>
+        <v/>
+      </c>
+      <c r="G43">
+        <f>F43/E42</f>
+        <v/>
+      </c>
+      <c r="H43" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I43">
+        <f>F43/H43</f>
         <v/>
       </c>
     </row>
@@ -5036,17 +5074,17 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -5054,21 +5092,21 @@
       <c r="D38" s="23" t="n">
         <v>46260</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="3" t="n">
         <v>2385318.77</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="3">
         <f>E38-E37</f>
         <v/>
       </c>
-      <c r="G38">
+      <c r="G38" s="3">
         <f>F38/E37</f>
         <v/>
       </c>
-      <c r="H38" t="n">
+      <c r="H38" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I38">
+      <c r="I38" s="3">
         <f>F38/H38</f>
         <v/>
       </c>
@@ -5254,11 +5292,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续3日增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-3+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5295,7 +5333,7 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I5" s="13">
@@ -5314,7 +5352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6873,17 +6911,17 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -6891,22 +6929,60 @@
       <c r="D42" s="23" t="n">
         <v>46260</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="3" t="n">
         <v>1872245.49</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="3">
         <f>E42-E41</f>
         <v/>
       </c>
-      <c r="G42">
+      <c r="G42" s="3">
         <f>F42/E41</f>
         <v/>
       </c>
-      <c r="H42" t="n">
+      <c r="H42" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="3">
         <f>F42/H42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1879145.49</v>
+      </c>
+      <c r="F43">
+        <f>E43-E42</f>
+        <v/>
+      </c>
+      <c r="G43">
+        <f>F43/E42</f>
+        <v/>
+      </c>
+      <c r="H43" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I43">
+        <f>F43/H43</f>
         <v/>
       </c>
     </row>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -1996,6 +1996,44 @@
       </c>
       <c r="I38" s="3">
         <f>F38/H38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D39" s="23" t="n">
+        <v>46262</v>
+      </c>
+      <c r="E39" t="n">
+        <v>682626.6800000001</v>
+      </c>
+      <c r="F39">
+        <f>E39-E38</f>
+        <v/>
+      </c>
+      <c r="G39">
+        <f>F39/E38</f>
+        <v/>
+      </c>
+      <c r="H39" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I39">
+        <f>F39/H39</f>
         <v/>
       </c>
     </row>
@@ -2010,7 +2048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3607,17 +3645,17 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -3625,22 +3663,60 @@
       <c r="D43" s="23" t="n">
         <v>46261</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="3" t="n">
         <v>628491.66</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="3">
         <f>E43-E42</f>
         <v/>
       </c>
-      <c r="G43">
+      <c r="G43" s="3">
         <f>F43/E42</f>
         <v/>
       </c>
-      <c r="H43" t="n">
+      <c r="H43" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I43">
+      <c r="I43" s="3">
         <f>F43/H43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="n">
+        <v>46262</v>
+      </c>
+      <c r="E44" t="n">
+        <v>626241.66</v>
+      </c>
+      <c r="F44">
+        <f>E44-E43</f>
+        <v/>
+      </c>
+      <c r="G44">
+        <f>F44/E43</f>
+        <v/>
+      </c>
+      <c r="H44" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I44">
+        <f>F44/H44</f>
         <v/>
       </c>
     </row>
@@ -3655,7 +3731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -5108,6 +5184,44 @@
       </c>
       <c r="I38" s="3">
         <f>F38/H38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D39" s="23" t="n">
+        <v>46262</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2329518.77</v>
+      </c>
+      <c r="F39">
+        <f>E39-E38</f>
+        <v/>
+      </c>
+      <c r="G39">
+        <f>F39/E38</f>
+        <v/>
+      </c>
+      <c r="H39" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I39">
+        <f>F39/H39</f>
         <v/>
       </c>
     </row>
@@ -5210,11 +5324,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>连续2日减持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-1+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-2+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5251,11 +5365,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>连续2日减持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-1+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-2+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5292,11 +5406,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>连续2日减持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5333,7 +5447,7 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I5" s="13">
@@ -5352,7 +5466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6949,17 +7063,17 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -6967,22 +7081,60 @@
       <c r="D43" s="23" t="n">
         <v>46261</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="3" t="n">
         <v>1879145.49</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="3">
         <f>E43-E42</f>
         <v/>
       </c>
-      <c r="G43">
+      <c r="G43" s="3">
         <f>F43/E42</f>
         <v/>
       </c>
-      <c r="H43" t="n">
+      <c r="H43" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I43">
+      <c r="I43" s="3">
         <f>F43/H43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="n">
+        <v>46262</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1876245.49</v>
+      </c>
+      <c r="F44">
+        <f>E44-E43</f>
+        <v/>
+      </c>
+      <c r="G44">
+        <f>F44/E43</f>
+        <v/>
+      </c>
+      <c r="H44" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I44">
+        <f>F44/H44</f>
         <v/>
       </c>
     </row>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2000,17 +2000,17 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2018,22 +2018,60 @@
       <c r="D39" s="23" t="n">
         <v>46262</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="3" t="n">
         <v>682626.6800000001</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="3">
         <f>E39-E38</f>
         <v/>
       </c>
-      <c r="G39">
+      <c r="G39" s="3">
         <f>F39/E38</f>
         <v/>
       </c>
-      <c r="H39" t="n">
+      <c r="H39" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="3">
         <f>F39/H39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E40" t="n">
+        <v>679386.6800000001</v>
+      </c>
+      <c r="F40">
+        <f>E40-E39</f>
+        <v/>
+      </c>
+      <c r="G40">
+        <f>F40/E39</f>
+        <v/>
+      </c>
+      <c r="H40" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I40">
+        <f>F40/H40</f>
         <v/>
       </c>
     </row>
@@ -2048,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3683,17 +3721,17 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -3701,22 +3739,60 @@
       <c r="D44" s="23" t="n">
         <v>46262</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="3" t="n">
         <v>626241.66</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="3">
         <f>E44-E43</f>
         <v/>
       </c>
-      <c r="G44">
+      <c r="G44" s="3">
         <f>F44/E43</f>
         <v/>
       </c>
-      <c r="H44" t="n">
+      <c r="H44" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I44">
+      <c r="I44" s="3">
         <f>F44/H44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D45" s="23" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E45" t="n">
+        <v>629841.66</v>
+      </c>
+      <c r="F45">
+        <f>E45-E44</f>
+        <v/>
+      </c>
+      <c r="G45">
+        <f>F45/E44</f>
+        <v/>
+      </c>
+      <c r="H45" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I45">
+        <f>F45/H45</f>
         <v/>
       </c>
     </row>
@@ -3731,7 +3807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -5188,17 +5264,17 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -5206,22 +5282,60 @@
       <c r="D39" s="23" t="n">
         <v>46262</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="3" t="n">
         <v>2329518.77</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="3">
         <f>E39-E38</f>
         <v/>
       </c>
-      <c r="G39">
+      <c r="G39" s="3">
         <f>F39/E38</f>
         <v/>
       </c>
-      <c r="H39" t="n">
+      <c r="H39" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="3">
         <f>F39/H39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2350398.77</v>
+      </c>
+      <c r="F40">
+        <f>E40-E39</f>
+        <v/>
+      </c>
+      <c r="G40">
+        <f>F40/E39</f>
+        <v/>
+      </c>
+      <c r="H40" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I40">
+        <f>F40/H40</f>
         <v/>
       </c>
     </row>
@@ -5324,11 +5438,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续2日减持</t>
+          <t>连续3日减持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-2+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-3+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5365,11 +5479,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续2日减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-2+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-1+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5406,11 +5520,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续2日减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5447,7 +5561,7 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I5" s="13">
@@ -5466,7 +5580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7101,17 +7215,17 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -7119,22 +7233,60 @@
       <c r="D44" s="23" t="n">
         <v>46262</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="3" t="n">
         <v>1876245.49</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="3">
         <f>E44-E43</f>
         <v/>
       </c>
-      <c r="G44">
+      <c r="G44" s="3">
         <f>F44/E43</f>
         <v/>
       </c>
-      <c r="H44" t="n">
+      <c r="H44" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I44">
+      <c r="I44" s="3">
         <f>F44/H44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D45" s="23" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1891645.49</v>
+      </c>
+      <c r="F45">
+        <f>E45-E44</f>
+        <v/>
+      </c>
+      <c r="G45">
+        <f>F45/E44</f>
+        <v/>
+      </c>
+      <c r="H45" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I45">
+        <f>F45/H45</f>
         <v/>
       </c>
     </row>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2038,17 +2038,17 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2056,21 +2056,21 @@
       <c r="D40" s="23" t="n">
         <v>46265</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="3" t="n">
         <v>679386.6800000001</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="3">
         <f>E40-E39</f>
         <v/>
       </c>
-      <c r="G40">
+      <c r="G40" s="3">
         <f>F40/E39</f>
         <v/>
       </c>
-      <c r="H40" t="n">
+      <c r="H40" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="3">
         <f>F40/H40</f>
         <v/>
       </c>
@@ -2086,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3759,17 +3759,17 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -3777,22 +3777,60 @@
       <c r="D45" s="23" t="n">
         <v>46265</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="3" t="n">
         <v>629841.66</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="3">
         <f>E45-E44</f>
         <v/>
       </c>
-      <c r="G45">
+      <c r="G45" s="3">
         <f>F45/E44</f>
         <v/>
       </c>
-      <c r="H45" t="n">
+      <c r="H45" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I45">
+      <c r="I45" s="3">
         <f>F45/H45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D46" s="23" t="n">
+        <v>46266</v>
+      </c>
+      <c r="E46" t="n">
+        <v>623001.66</v>
+      </c>
+      <c r="F46">
+        <f>E46-E45</f>
+        <v/>
+      </c>
+      <c r="G46">
+        <f>F46/E45</f>
+        <v/>
+      </c>
+      <c r="H46" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I46">
+        <f>F46/H46</f>
         <v/>
       </c>
     </row>
@@ -5302,17 +5340,17 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -5320,21 +5358,21 @@
       <c r="D40" s="23" t="n">
         <v>46265</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="3" t="n">
         <v>2350398.77</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="3">
         <f>E40-E39</f>
         <v/>
       </c>
-      <c r="G40">
+      <c r="G40" s="3">
         <f>F40/E39</f>
         <v/>
       </c>
-      <c r="H40" t="n">
+      <c r="H40" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="3">
         <f>F40/H40</f>
         <v/>
       </c>
@@ -5520,7 +5558,7 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I4" s="13">
@@ -5561,11 +5599,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>连续2日增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-1+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-2+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5580,7 +5618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7253,17 +7291,17 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -7271,22 +7309,60 @@
       <c r="D45" s="23" t="n">
         <v>46265</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="3" t="n">
         <v>1891645.49</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="3">
         <f>E45-E44</f>
         <v/>
       </c>
-      <c r="G45">
+      <c r="G45" s="3">
         <f>F45/E44</f>
         <v/>
       </c>
-      <c r="H45" t="n">
+      <c r="H45" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I45">
+      <c r="I45" s="3">
         <f>F45/H45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D46" s="23" t="n">
+        <v>46266</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1904445.49</v>
+      </c>
+      <c r="F46">
+        <f>E46-E45</f>
+        <v/>
+      </c>
+      <c r="G46">
+        <f>F46/E45</f>
+        <v/>
+      </c>
+      <c r="H46" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I46">
+        <f>F46/H46</f>
         <v/>
       </c>
     </row>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2072,6 +2072,44 @@
       </c>
       <c r="I40" s="3">
         <f>F40/H40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="n">
+        <v>46266</v>
+      </c>
+      <c r="E41" t="n">
+        <v>653376.6800000001</v>
+      </c>
+      <c r="F41">
+        <f>E41-E40</f>
+        <v/>
+      </c>
+      <c r="G41">
+        <f>F41/E40</f>
+        <v/>
+      </c>
+      <c r="H41" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I41">
+        <f>F41/H41</f>
         <v/>
       </c>
     </row>
@@ -3797,17 +3835,17 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -3815,21 +3853,21 @@
       <c r="D46" s="23" t="n">
         <v>46266</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="3" t="n">
         <v>623001.66</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="3">
         <f>E46-E45</f>
         <v/>
       </c>
-      <c r="G46">
+      <c r="G46" s="3">
         <f>F46/E45</f>
         <v/>
       </c>
-      <c r="H46" t="n">
+      <c r="H46" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I46">
+      <c r="I46" s="3">
         <f>F46/H46</f>
         <v/>
       </c>
@@ -3845,7 +3883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -5374,6 +5412,44 @@
       </c>
       <c r="I40" s="3">
         <f>F40/H40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="n">
+        <v>46266</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2299998.77</v>
+      </c>
+      <c r="F41">
+        <f>E41-E40</f>
+        <v/>
+      </c>
+      <c r="G41">
+        <f>F41/E40</f>
+        <v/>
+      </c>
+      <c r="H41" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I41">
+        <f>F41/H41</f>
         <v/>
       </c>
     </row>
@@ -5476,11 +5552,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续3日减持</t>
+          <t>连续4日减持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-3+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-4+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5517,7 +5593,7 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I3" s="13">
@@ -7329,17 +7405,17 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -7347,21 +7423,21 @@
       <c r="D46" s="23" t="n">
         <v>46266</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="3" t="n">
         <v>1904445.49</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="3">
         <f>E46-E45</f>
         <v/>
       </c>
-      <c r="G46">
+      <c r="G46" s="3">
         <f>F46/E45</f>
         <v/>
       </c>
-      <c r="H46" t="n">
+      <c r="H46" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I46">
+      <c r="I46" s="3">
         <f>F46/H46</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2076,17 +2076,17 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2094,22 +2094,60 @@
       <c r="D41" s="23" t="n">
         <v>46266</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="3" t="n">
         <v>653376.6800000001</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="3">
         <f>E41-E40</f>
         <v/>
       </c>
-      <c r="G41">
+      <c r="G41" s="3">
         <f>F41/E40</f>
         <v/>
       </c>
-      <c r="H41" t="n">
+      <c r="H41" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I41">
+      <c r="I41" s="3">
         <f>F41/H41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E42" t="n">
+        <v>647256.6800000001</v>
+      </c>
+      <c r="F42">
+        <f>E42-E41</f>
+        <v/>
+      </c>
+      <c r="G42">
+        <f>F42/E41</f>
+        <v/>
+      </c>
+      <c r="H42" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I42">
+        <f>F42/H42</f>
         <v/>
       </c>
     </row>
@@ -3883,7 +3921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -5416,17 +5454,17 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -5434,22 +5472,60 @@
       <c r="D41" s="23" t="n">
         <v>46266</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="3" t="n">
         <v>2299998.77</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="3">
         <f>E41-E40</f>
         <v/>
       </c>
-      <c r="G41">
+      <c r="G41" s="3">
         <f>F41/E40</f>
         <v/>
       </c>
-      <c r="H41" t="n">
+      <c r="H41" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I41">
+      <c r="I41" s="3">
         <f>F41/H41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2295678.77</v>
+      </c>
+      <c r="F42">
+        <f>E42-E41</f>
+        <v/>
+      </c>
+      <c r="G42">
+        <f>F42/E41</f>
+        <v/>
+      </c>
+      <c r="H42" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I42">
+        <f>F42/H42</f>
         <v/>
       </c>
     </row>
@@ -5552,11 +5628,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续4日减持</t>
+          <t>连续5日减持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-4+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-5+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5593,11 +5669,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>连续2日减持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-1+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-2+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2114,17 +2114,17 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2132,21 +2132,21 @@
       <c r="D42" s="23" t="n">
         <v>46267</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="3" t="n">
         <v>647256.6800000001</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="3">
         <f>E42-E41</f>
         <v/>
       </c>
-      <c r="G42">
+      <c r="G42" s="3">
         <f>F42/E41</f>
         <v/>
       </c>
-      <c r="H42" t="n">
+      <c r="H42" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="3">
         <f>F42/H42</f>
         <v/>
       </c>
@@ -2162,7 +2162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3907,6 +3907,44 @@
       </c>
       <c r="I46" s="3">
         <f>F46/H46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E47" t="n">
+        <v>622641.66</v>
+      </c>
+      <c r="F47">
+        <f>E47-E46</f>
+        <v/>
+      </c>
+      <c r="G47">
+        <f>F47/E46</f>
+        <v/>
+      </c>
+      <c r="H47" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I47">
+        <f>F47/H47</f>
         <v/>
       </c>
     </row>
@@ -5492,17 +5530,17 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -5510,21 +5548,21 @@
       <c r="D42" s="23" t="n">
         <v>46267</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="3" t="n">
         <v>2295678.77</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="3">
         <f>E42-E41</f>
         <v/>
       </c>
-      <c r="G42">
+      <c r="G42" s="3">
         <f>F42/E41</f>
         <v/>
       </c>
-      <c r="H42" t="n">
+      <c r="H42" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="3">
         <f>F42/H42</f>
         <v/>
       </c>
@@ -5710,11 +5748,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>连续2日减持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5751,11 +5789,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续2日增持</t>
+          <t>连续3日增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-2+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-3+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5770,7 +5808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7518,6 +7556,44 @@
         <v/>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1948045.49</v>
+      </c>
+      <c r="F47">
+        <f>E47-E46</f>
+        <v/>
+      </c>
+      <c r="G47">
+        <f>F47/E46</f>
+        <v/>
+      </c>
+      <c r="H47" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I47">
+        <f>F47/H47</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2148,6 +2148,44 @@
       </c>
       <c r="I42" s="3">
         <f>F42/H42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="n">
+        <v>46268</v>
+      </c>
+      <c r="E43" t="n">
+        <v>656076.6800000001</v>
+      </c>
+      <c r="F43">
+        <f>E43-E42</f>
+        <v/>
+      </c>
+      <c r="G43">
+        <f>F43/E42</f>
+        <v/>
+      </c>
+      <c r="H43" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I43">
+        <f>F43/H43</f>
         <v/>
       </c>
     </row>
@@ -3911,17 +3949,17 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -3929,21 +3967,21 @@
       <c r="D47" s="23" t="n">
         <v>46267</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="3" t="n">
         <v>622641.66</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="3">
         <f>E47-E46</f>
         <v/>
       </c>
-      <c r="G47">
+      <c r="G47" s="3">
         <f>F47/E46</f>
         <v/>
       </c>
-      <c r="H47" t="n">
+      <c r="H47" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I47">
+      <c r="I47" s="3">
         <f>F47/H47</f>
         <v/>
       </c>
@@ -3959,7 +3997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -5564,6 +5602,44 @@
       </c>
       <c r="I42" s="3">
         <f>F42/H42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="n">
+        <v>46268</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2312058.77</v>
+      </c>
+      <c r="F43">
+        <f>E43-E42</f>
+        <v/>
+      </c>
+      <c r="G43">
+        <f>F43/E42</f>
+        <v/>
+      </c>
+      <c r="H43" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I43">
+        <f>F43/H43</f>
         <v/>
       </c>
     </row>
@@ -5666,11 +5742,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续5日减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-5+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-1+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5707,11 +5783,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续2日减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-2+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-1+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7557,17 +7633,17 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -7575,21 +7651,21 @@
       <c r="D47" s="23" t="n">
         <v>46267</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="3" t="n">
         <v>1948045.49</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="3">
         <f>E47-E46</f>
         <v/>
       </c>
-      <c r="G47">
+      <c r="G47" s="3">
         <f>F47/E46</f>
         <v/>
       </c>
-      <c r="H47" t="n">
+      <c r="H47" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I47">
+      <c r="I47" s="3">
         <f>F47/H47</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2152,17 +2152,17 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2170,21 +2170,21 @@
       <c r="D43" s="23" t="n">
         <v>46268</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="3" t="n">
         <v>656076.6800000001</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="3">
         <f>E43-E42</f>
         <v/>
       </c>
-      <c r="G43">
+      <c r="G43" s="3">
         <f>F43/E42</f>
         <v/>
       </c>
-      <c r="H43" t="n">
+      <c r="H43" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I43">
+      <c r="I43" s="3">
         <f>F43/H43</f>
         <v/>
       </c>
@@ -2200,7 +2200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3983,6 +3983,44 @@
       </c>
       <c r="I47" s="3">
         <f>F47/H47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D48" s="23" t="n">
+        <v>46268</v>
+      </c>
+      <c r="E48" t="n">
+        <v>623541.66</v>
+      </c>
+      <c r="F48">
+        <f>E48-E47</f>
+        <v/>
+      </c>
+      <c r="G48">
+        <f>F48/E47</f>
+        <v/>
+      </c>
+      <c r="H48" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I48">
+        <f>F48/H48</f>
         <v/>
       </c>
     </row>
@@ -5606,17 +5644,17 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -5624,21 +5662,21 @@
       <c r="D43" s="23" t="n">
         <v>46268</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="3" t="n">
         <v>2312058.77</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="3">
         <f>E43-E42</f>
         <v/>
       </c>
-      <c r="G43">
+      <c r="G43" s="3">
         <f>F43/E42</f>
         <v/>
       </c>
-      <c r="H43" t="n">
+      <c r="H43" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I43">
+      <c r="I43" s="3">
         <f>F43/H43</f>
         <v/>
       </c>
@@ -5824,11 +5862,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续2日减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5865,11 +5903,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续3日增持</t>
+          <t>连续4日增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-3+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-4+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5884,7 +5922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7670,6 +7708,44 @@
         <v/>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D48" s="23" t="n">
+        <v>46268</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1982845.49</v>
+      </c>
+      <c r="F48">
+        <f>E48-E47</f>
+        <v/>
+      </c>
+      <c r="G48">
+        <f>F48/E47</f>
+        <v/>
+      </c>
+      <c r="H48" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I48">
+        <f>F48/H48</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -3987,17 +3987,17 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -4005,21 +4005,21 @@
       <c r="D48" s="23" t="n">
         <v>46268</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="3" t="n">
         <v>623541.66</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="3">
         <f>E48-E47</f>
         <v/>
       </c>
-      <c r="G48">
+      <c r="G48" s="3">
         <f>F48/E47</f>
         <v/>
       </c>
-      <c r="H48" t="n">
+      <c r="H48" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I48">
+      <c r="I48" s="3">
         <f>F48/H48</f>
         <v/>
       </c>
@@ -7709,17 +7709,17 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -7727,21 +7727,21 @@
       <c r="D48" s="23" t="n">
         <v>46268</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="3" t="n">
         <v>1982845.49</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="3">
         <f>E48-E47</f>
         <v/>
       </c>
-      <c r="G48">
+      <c r="G48" s="3">
         <f>F48/E47</f>
         <v/>
       </c>
-      <c r="H48" t="n">
+      <c r="H48" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I48">
+      <c r="I48" s="3">
         <f>F48/H48</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2186,6 +2186,44 @@
       </c>
       <c r="I43" s="3">
         <f>F43/H43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="n">
+        <v>46269</v>
+      </c>
+      <c r="E44" t="n">
+        <v>681096.6800000001</v>
+      </c>
+      <c r="F44">
+        <f>E44-E43</f>
+        <v/>
+      </c>
+      <c r="G44">
+        <f>F44/E43</f>
+        <v/>
+      </c>
+      <c r="H44" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I44">
+        <f>F44/H44</f>
         <v/>
       </c>
     </row>
@@ -2200,7 +2238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4021,6 +4059,44 @@
       </c>
       <c r="I48" s="3">
         <f>F48/H48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D49" s="23" t="n">
+        <v>46269</v>
+      </c>
+      <c r="E49" t="n">
+        <v>625341.66</v>
+      </c>
+      <c r="F49">
+        <f>E49-E48</f>
+        <v/>
+      </c>
+      <c r="G49">
+        <f>F49/E48</f>
+        <v/>
+      </c>
+      <c r="H49" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I49">
+        <f>F49/H49</f>
         <v/>
       </c>
     </row>
@@ -4035,7 +4111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -5678,6 +5754,44 @@
       </c>
       <c r="I43" s="3">
         <f>F43/H43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="n">
+        <v>46269</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2337708.77</v>
+      </c>
+      <c r="F44">
+        <f>E44-E43</f>
+        <v/>
+      </c>
+      <c r="G44">
+        <f>F44/E43</f>
+        <v/>
+      </c>
+      <c r="H44" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I44">
+        <f>F44/H44</f>
         <v/>
       </c>
     </row>
@@ -5780,11 +5894,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>连续2日增持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-1+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-2+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5821,11 +5935,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>连续2日增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-1+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-2+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5862,11 +5976,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>连续2日增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5903,11 +6017,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续4日增持</t>
+          <t>连续5日增持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-4+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-5+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5922,7 +6036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7746,6 +7860,44 @@
         <v/>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D49" s="23" t="n">
+        <v>46269</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2008945.49</v>
+      </c>
+      <c r="F49">
+        <f>E49-E48</f>
+        <v/>
+      </c>
+      <c r="G49">
+        <f>F49/E48</f>
+        <v/>
+      </c>
+      <c r="H49" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I49">
+        <f>F49/H49</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2190,17 +2190,17 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2208,21 +2208,21 @@
       <c r="D44" s="23" t="n">
         <v>46269</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="3" t="n">
         <v>681096.6800000001</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="3">
         <f>E44-E43</f>
         <v/>
       </c>
-      <c r="G44">
+      <c r="G44" s="3">
         <f>F44/E43</f>
         <v/>
       </c>
-      <c r="H44" t="n">
+      <c r="H44" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I44">
+      <c r="I44" s="3">
         <f>F44/H44</f>
         <v/>
       </c>
@@ -4063,17 +4063,17 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -4081,21 +4081,21 @@
       <c r="D49" s="23" t="n">
         <v>46269</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="3" t="n">
         <v>625341.66</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="3">
         <f>E49-E48</f>
         <v/>
       </c>
-      <c r="G49">
+      <c r="G49" s="3">
         <f>F49/E48</f>
         <v/>
       </c>
-      <c r="H49" t="n">
+      <c r="H49" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I49">
+      <c r="I49" s="3">
         <f>F49/H49</f>
         <v/>
       </c>
@@ -5758,17 +5758,17 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -5776,21 +5776,21 @@
       <c r="D44" s="23" t="n">
         <v>46269</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="3" t="n">
         <v>2337708.77</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="3">
         <f>E44-E43</f>
         <v/>
       </c>
-      <c r="G44">
+      <c r="G44" s="3">
         <f>F44/E43</f>
         <v/>
       </c>
-      <c r="H44" t="n">
+      <c r="H44" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I44">
+      <c r="I44" s="3">
         <f>F44/H44</f>
         <v/>
       </c>
@@ -7861,17 +7861,17 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -7879,21 +7879,21 @@
       <c r="D49" s="23" t="n">
         <v>46269</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="3" t="n">
         <v>2008945.49</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="3">
         <f>E49-E48</f>
         <v/>
       </c>
-      <c r="G49">
+      <c r="G49" s="3">
         <f>F49/E48</f>
         <v/>
       </c>
-      <c r="H49" t="n">
+      <c r="H49" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I49">
+      <c r="I49" s="3">
         <f>F49/H49</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2238,7 +2238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4097,6 +4097,44 @@
       </c>
       <c r="I49" s="3">
         <f>F49/H49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D50" s="23" t="n">
+        <v>46272</v>
+      </c>
+      <c r="E50" t="n">
+        <v>628761.66</v>
+      </c>
+      <c r="F50">
+        <f>E50-E49</f>
+        <v/>
+      </c>
+      <c r="G50">
+        <f>F50/E49</f>
+        <v/>
+      </c>
+      <c r="H50" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I50">
+        <f>F50/H50</f>
         <v/>
       </c>
     </row>
@@ -5976,11 +6014,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续2日增持</t>
+          <t>连续3日增持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-3+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6017,11 +6055,11 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>连续5日增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I5" s="13">
-        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-5+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
+        <f>SUM(INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)-1+1):INDEX('159915'!$I:$I,COUNTA('159915'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6036,7 +6074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7898,6 +7936,44 @@
         <v/>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D50" s="23" t="n">
+        <v>46272</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1929145.49</v>
+      </c>
+      <c r="F50">
+        <f>E50-E49</f>
+        <v/>
+      </c>
+      <c r="G50">
+        <f>F50/E49</f>
+        <v/>
+      </c>
+      <c r="H50" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I50">
+        <f>F50/H50</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2224,6 +2224,44 @@
       </c>
       <c r="I44" s="3">
         <f>F44/H44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D45" s="23" t="n">
+        <v>46272</v>
+      </c>
+      <c r="E45" t="n">
+        <v>701886.6800000001</v>
+      </c>
+      <c r="F45">
+        <f>E45-E44</f>
+        <v/>
+      </c>
+      <c r="G45">
+        <f>F45/E44</f>
+        <v/>
+      </c>
+      <c r="H45" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I45">
+        <f>F45/H45</f>
         <v/>
       </c>
     </row>
@@ -4101,17 +4139,17 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -4119,21 +4157,21 @@
       <c r="D50" s="23" t="n">
         <v>46272</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="3" t="n">
         <v>628761.66</v>
       </c>
-      <c r="F50">
+      <c r="F50" s="3">
         <f>E50-E49</f>
         <v/>
       </c>
-      <c r="G50">
+      <c r="G50" s="3">
         <f>F50/E49</f>
         <v/>
       </c>
-      <c r="H50" t="n">
+      <c r="H50" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I50">
+      <c r="I50" s="3">
         <f>F50/H50</f>
         <v/>
       </c>
@@ -4149,7 +4187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -5830,6 +5868,44 @@
       </c>
       <c r="I44" s="3">
         <f>F44/H44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D45" s="23" t="n">
+        <v>46272</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2364888.77</v>
+      </c>
+      <c r="F45">
+        <f>E45-E44</f>
+        <v/>
+      </c>
+      <c r="G45">
+        <f>F45/E44</f>
+        <v/>
+      </c>
+      <c r="H45" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I45">
+        <f>F45/H45</f>
         <v/>
       </c>
     </row>
@@ -5932,11 +6008,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续2日增持</t>
+          <t>连续3日增持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-2+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-3+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -5973,11 +6049,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续2日增持</t>
+          <t>连续3日增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-2+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-3+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -7937,17 +8013,17 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -7955,21 +8031,21 @@
       <c r="D50" s="23" t="n">
         <v>46272</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="3" t="n">
         <v>1929145.49</v>
       </c>
-      <c r="F50">
+      <c r="F50" s="3">
         <f>E50-E49</f>
         <v/>
       </c>
-      <c r="G50">
+      <c r="G50" s="3">
         <f>F50/E49</f>
         <v/>
       </c>
-      <c r="H50" t="n">
+      <c r="H50" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I50">
+      <c r="I50" s="3">
         <f>F50/H50</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2228,17 +2228,17 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2246,22 +2246,60 @@
       <c r="D45" s="23" t="n">
         <v>46272</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="3" t="n">
         <v>701886.6800000001</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="3">
         <f>E45-E44</f>
         <v/>
       </c>
-      <c r="G45">
+      <c r="G45" s="3">
         <f>F45/E44</f>
         <v/>
       </c>
-      <c r="H45" t="n">
+      <c r="H45" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I45">
+      <c r="I45" s="3">
         <f>F45/H45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D46" s="23" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E46" t="n">
+        <v>684786.6800000001</v>
+      </c>
+      <c r="F46">
+        <f>E46-E45</f>
+        <v/>
+      </c>
+      <c r="G46">
+        <f>F46/E45</f>
+        <v/>
+      </c>
+      <c r="H46" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I46">
+        <f>F46/H46</f>
         <v/>
       </c>
     </row>
@@ -2276,7 +2314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4173,6 +4211,44 @@
       </c>
       <c r="I50" s="3">
         <f>F50/H50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D51" s="23" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E51" t="n">
+        <v>625701.66</v>
+      </c>
+      <c r="F51">
+        <f>E51-E50</f>
+        <v/>
+      </c>
+      <c r="G51">
+        <f>F51/E50</f>
+        <v/>
+      </c>
+      <c r="H51" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I51">
+        <f>F51/H51</f>
         <v/>
       </c>
     </row>
@@ -4187,7 +4263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -5872,17 +5948,17 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -5890,22 +5966,60 @@
       <c r="D45" s="23" t="n">
         <v>46272</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="3" t="n">
         <v>2364888.77</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="3">
         <f>E45-E44</f>
         <v/>
       </c>
-      <c r="G45">
+      <c r="G45" s="3">
         <f>F45/E44</f>
         <v/>
       </c>
-      <c r="H45" t="n">
+      <c r="H45" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I45">
+      <c r="I45" s="3">
         <f>F45/H45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D46" s="23" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2346888.77</v>
+      </c>
+      <c r="F46">
+        <f>E46-E45</f>
+        <v/>
+      </c>
+      <c r="G46">
+        <f>F46/E45</f>
+        <v/>
+      </c>
+      <c r="H46" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I46">
+        <f>F46/H46</f>
         <v/>
       </c>
     </row>
@@ -6008,11 +6122,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续3日增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-3+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-1+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6049,11 +6163,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续3日增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-3+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-1+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6090,11 +6204,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续3日增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-3+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6131,7 +6245,7 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I5" s="13">
@@ -6150,7 +6264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8050,6 +8164,44 @@
         <v/>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D51" s="23" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1936445.49</v>
+      </c>
+      <c r="F51">
+        <f>E51-E50</f>
+        <v/>
+      </c>
+      <c r="G51">
+        <f>F51/E50</f>
+        <v/>
+      </c>
+      <c r="H51" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I51">
+        <f>F51/H51</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2266,17 +2266,17 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2284,21 +2284,21 @@
       <c r="D46" s="23" t="n">
         <v>46273</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="3" t="n">
         <v>684786.6800000001</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="3">
         <f>E46-E45</f>
         <v/>
       </c>
-      <c r="G46">
+      <c r="G46" s="3">
         <f>F46/E45</f>
         <v/>
       </c>
-      <c r="H46" t="n">
+      <c r="H46" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I46">
+      <c r="I46" s="3">
         <f>F46/H46</f>
         <v/>
       </c>
@@ -4215,17 +4215,17 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -4233,21 +4233,21 @@
       <c r="D51" s="23" t="n">
         <v>46273</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="3" t="n">
         <v>625701.66</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="3">
         <f>E51-E50</f>
         <v/>
       </c>
-      <c r="G51">
+      <c r="G51" s="3">
         <f>F51/E50</f>
         <v/>
       </c>
-      <c r="H51" t="n">
+      <c r="H51" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I51">
+      <c r="I51" s="3">
         <f>F51/H51</f>
         <v/>
       </c>
@@ -5986,17 +5986,17 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -6004,21 +6004,21 @@
       <c r="D46" s="23" t="n">
         <v>46273</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="3" t="n">
         <v>2346888.77</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="3">
         <f>E46-E45</f>
         <v/>
       </c>
-      <c r="G46">
+      <c r="G46" s="3">
         <f>F46/E45</f>
         <v/>
       </c>
-      <c r="H46" t="n">
+      <c r="H46" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I46">
+      <c r="I46" s="3">
         <f>F46/H46</f>
         <v/>
       </c>
@@ -8165,17 +8165,17 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -8183,21 +8183,21 @@
       <c r="D51" s="23" t="n">
         <v>46273</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="3" t="n">
         <v>1936445.49</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="3">
         <f>E51-E50</f>
         <v/>
       </c>
-      <c r="G51">
+      <c r="G51" s="3">
         <f>F51/E50</f>
         <v/>
       </c>
-      <c r="H51" t="n">
+      <c r="H51" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I51">
+      <c r="I51" s="3">
         <f>F51/H51</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2300,6 +2300,44 @@
       </c>
       <c r="I46" s="3">
         <f>F46/H46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E47" t="n">
+        <v>684696.6800000001</v>
+      </c>
+      <c r="F47">
+        <f>E47-E46</f>
+        <v/>
+      </c>
+      <c r="G47">
+        <f>F47/E46</f>
+        <v/>
+      </c>
+      <c r="H47" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I47">
+        <f>F47/H47</f>
         <v/>
       </c>
     </row>
@@ -2314,7 +2352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4249,6 +4287,44 @@
       </c>
       <c r="I51" s="3">
         <f>F51/H51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D52" s="23" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E52" t="n">
+        <v>624711.66</v>
+      </c>
+      <c r="F52">
+        <f>E52-E51</f>
+        <v/>
+      </c>
+      <c r="G52">
+        <f>F52/E51</f>
+        <v/>
+      </c>
+      <c r="H52" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I52">
+        <f>F52/H52</f>
         <v/>
       </c>
     </row>
@@ -4263,7 +4339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -6020,6 +6096,44 @@
       </c>
       <c r="I46" s="3">
         <f>F46/H46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2318538.77</v>
+      </c>
+      <c r="F47">
+        <f>E47-E46</f>
+        <v/>
+      </c>
+      <c r="G47">
+        <f>F47/E46</f>
+        <v/>
+      </c>
+      <c r="H47" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I47">
+        <f>F47/H47</f>
         <v/>
       </c>
     </row>
@@ -6122,11 +6236,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>连续2日减持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-1+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-2+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6163,11 +6277,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>连续2日减持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-1+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-2+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6204,11 +6318,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>连续2日减持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-1+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6245,7 +6359,7 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>反转增持</t>
+          <t>反转减持</t>
         </is>
       </c>
       <c r="I5" s="13">
@@ -6264,7 +6378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8202,6 +8316,44 @@
         <v/>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D52" s="23" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1935645.49</v>
+      </c>
+      <c r="F52">
+        <f>E52-E51</f>
+        <v/>
+      </c>
+      <c r="G52">
+        <f>F52/E51</f>
+        <v/>
+      </c>
+      <c r="H52" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I52">
+        <f>F52/H52</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2304,17 +2304,17 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2322,21 +2322,21 @@
       <c r="D47" s="23" t="n">
         <v>46274</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="3" t="n">
         <v>684696.6800000001</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="3">
         <f>E47-E46</f>
         <v/>
       </c>
-      <c r="G47">
+      <c r="G47" s="3">
         <f>F47/E46</f>
         <v/>
       </c>
-      <c r="H47" t="n">
+      <c r="H47" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I47">
+      <c r="I47" s="3">
         <f>F47/H47</f>
         <v/>
       </c>
@@ -4291,17 +4291,17 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -4309,21 +4309,21 @@
       <c r="D52" s="23" t="n">
         <v>46274</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" s="3" t="n">
         <v>624711.66</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="3">
         <f>E52-E51</f>
         <v/>
       </c>
-      <c r="G52">
+      <c r="G52" s="3">
         <f>F52/E51</f>
         <v/>
       </c>
-      <c r="H52" t="n">
+      <c r="H52" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I52">
+      <c r="I52" s="3">
         <f>F52/H52</f>
         <v/>
       </c>
@@ -6100,17 +6100,17 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -6118,21 +6118,21 @@
       <c r="D47" s="23" t="n">
         <v>46274</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="3" t="n">
         <v>2318538.77</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="3">
         <f>E47-E46</f>
         <v/>
       </c>
-      <c r="G47">
+      <c r="G47" s="3">
         <f>F47/E46</f>
         <v/>
       </c>
-      <c r="H47" t="n">
+      <c r="H47" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I47">
+      <c r="I47" s="3">
         <f>F47/H47</f>
         <v/>
       </c>
@@ -8317,17 +8317,17 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -8335,21 +8335,21 @@
       <c r="D52" s="23" t="n">
         <v>46274</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" s="3" t="n">
         <v>1935645.49</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="3">
         <f>E52-E51</f>
         <v/>
       </c>
-      <c r="G52">
+      <c r="G52" s="3">
         <f>F52/E51</f>
         <v/>
       </c>
-      <c r="H52" t="n">
+      <c r="H52" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I52">
+      <c r="I52" s="3">
         <f>F52/H52</f>
         <v/>
       </c>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828" customWidth="1" style="17" min="9" max="9"/>
@@ -2338,6 +2338,44 @@
       </c>
       <c r="I47" s="3">
         <f>F47/H47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>510050</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>上证50华夏</t>
+        </is>
+      </c>
+      <c r="D48" s="23" t="n">
+        <v>46275</v>
+      </c>
+      <c r="E48" t="n">
+        <v>671826.6800000001</v>
+      </c>
+      <c r="F48">
+        <f>E48-E47</f>
+        <v/>
+      </c>
+      <c r="G48">
+        <f>F48/E47</f>
+        <v/>
+      </c>
+      <c r="H48" t="n">
+        <v>5666466.68</v>
+      </c>
+      <c r="I48">
+        <f>F48/H48</f>
         <v/>
       </c>
     </row>
@@ -2352,7 +2390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4325,6 +4363,44 @@
       </c>
       <c r="I52" s="3">
         <f>F52/H52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>159919</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>沪深300ETF嘉实</t>
+        </is>
+      </c>
+      <c r="D53" s="23" t="n">
+        <v>46275</v>
+      </c>
+      <c r="E53" t="n">
+        <v>624351.66</v>
+      </c>
+      <c r="F53">
+        <f>E53-E52</f>
+        <v/>
+      </c>
+      <c r="G53">
+        <f>F53/E52</f>
+        <v/>
+      </c>
+      <c r="H53" t="n">
+        <v>4081881.66</v>
+      </c>
+      <c r="I53">
+        <f>F53/H53</f>
         <v/>
       </c>
     </row>
@@ -4339,7 +4415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.49219" customWidth="1" style="20" min="1" max="1"/>
@@ -6134,6 +6210,44 @@
       </c>
       <c r="I47" s="3">
         <f>F47/H47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>沪深300etf华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D48" s="23" t="n">
+        <v>46275</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2319078.77</v>
+      </c>
+      <c r="F48">
+        <f>E48-E47</f>
+        <v/>
+      </c>
+      <c r="G48">
+        <f>F48/E47</f>
+        <v/>
+      </c>
+      <c r="H48" t="n">
+        <v>8882958.77</v>
+      </c>
+      <c r="I48">
+        <f>F48/H48</f>
         <v/>
       </c>
     </row>
@@ -6236,11 +6350,11 @@
       </c>
       <c r="H2" s="20" t="inlineStr">
         <is>
-          <t>连续2日减持</t>
+          <t>连续3日减持</t>
         </is>
       </c>
       <c r="I2" s="13">
-        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-2+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
+        <f>SUM(INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)-3+1):INDEX('510050'!$I:$I,COUNTA('510050'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6277,11 +6391,11 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>连续2日减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I3" s="13">
-        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-2+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
+        <f>SUM(INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)-1+1):INDEX('510300'!$I:$I,COUNTA('510300'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6318,11 +6432,11 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>连续2日减持</t>
+          <t>连续3日减持</t>
         </is>
       </c>
       <c r="I4" s="13">
-        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-2+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
+        <f>SUM(INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)-3+1):INDEX('159919'!$I:$I,COUNTA('159919'!$E:$E)))</f>
         <v/>
       </c>
     </row>
@@ -6359,7 +6473,7 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>反转减持</t>
+          <t>反转增持</t>
         </is>
       </c>
       <c r="I5" s="13">
@@ -6378,7 +6492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8354,6 +8468,44 @@
         <v/>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>易方达创业板ETF</t>
+        </is>
+      </c>
+      <c r="D53" s="23" t="n">
+        <v>46275</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1944845.49</v>
+      </c>
+      <c r="F53">
+        <f>E53-E52</f>
+        <v/>
+      </c>
+      <c r="G53">
+        <f>F53/E52</f>
+        <v/>
+      </c>
+      <c r="H53" t="n">
+        <v>3150245.49</v>
+      </c>
+      <c r="I53">
+        <f>F53/H53</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf跟踪.xlsx
+++ b/etf跟踪.xlsx
@@ -2342,17 +2342,17 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>510050</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>上证50华夏</t>
         </is>
@@ -2360,21 +2360,21 @@
       <c r="D48" s="23" t="n">
         <v>46275</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="3" t="n">
         <v>671826.6800000001</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="3">
         <f>E48-E47</f>
         <v/>
       </c>
-      <c r="G48">
+      <c r="G48" s="3">
         <f>F48/E47</f>
         <v/>
       </c>
-      <c r="H48" t="n">
+      <c r="H48" s="3" t="n">
         <v>5666466.68</v>
       </c>
-      <c r="I48">
+      <c r="I48" s="3">
         <f>F48/H48</f>
         <v/>
       </c>
@@ -4367,17 +4367,17 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>159919</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>沪深300ETF嘉实</t>
         </is>
@@ -4385,21 +4385,21 @@
       <c r="D53" s="23" t="n">
         <v>46275</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" s="3" t="n">
         <v>624351.66</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="3">
         <f>E53-E52</f>
         <v/>
       </c>
-      <c r="G53">
+      <c r="G53" s="3">
         <f>F53/E52</f>
         <v/>
       </c>
-      <c r="H53" t="n">
+      <c r="H53" s="3" t="n">
         <v>4081881.66</v>
       </c>
-      <c r="I53">
+      <c r="I53" s="3">
         <f>F53/H53</f>
         <v/>
       </c>
@@ -6214,17 +6214,17 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>沪深300etf华泰柏瑞</t>
         </is>
@@ -6232,21 +6232,21 @@
       <c r="D48" s="23" t="n">
         <v>46275</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="3" t="n">
         <v>2319078.77</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="3">
         <f>E48-E47</f>
         <v/>
       </c>
-      <c r="G48">
+      <c r="G48" s="3">
         <f>F48/E47</f>
         <v/>
       </c>
-      <c r="H48" t="n">
+      <c r="H48" s="3" t="n">
         <v>8882958.77</v>
       </c>
-      <c r="I48">
+      <c r="I48" s="3">
         <f>F48/H48</f>
         <v/>
       </c>
@@ -8469,17 +8469,17 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
@@ -8487,21 +8487,21 @@
       <c r="D53" s="23" t="n">
         <v>46275</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" s="3" t="n">
         <v>1944845.49</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="3">
         <f>E53-E52</f>
         <v/>
       </c>
-      <c r="G53">
+      <c r="G53" s="3">
         <f>F53/E52</f>
         <v/>
       </c>
-      <c r="H53" t="n">
+      <c r="H53" s="3" t="n">
         <v>3150245.49</v>
       </c>
-      <c r="I53">
+      <c r="I53" s="3">
         <f>F53/H53</f>
         <v/>
       </c>
